--- a/sheets/Produccion_Sheet_Plantilla.xlsx
+++ b/sheets/Produccion_Sheet_Plantilla.xlsx
@@ -9,11 +9,12 @@
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Órdenes de Despacho" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Órdenes de Ingreso" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Inventario" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Cortes" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Precosteo Referencias" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Orden de Corte (formato)" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Precosteo (formato)" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Histórico Precosteo" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Orden de Corte (formato)" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -50,7 +51,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Lo genera el sistema (Code128) para la etiqueta.</t>
+          <t xml:space="preserve">Lo genera el sistema (Code128).</t>
         </r>
       </text>
     </comment>
@@ -80,74 +81,16 @@
 </comments>
 </file>
 
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <authors>
-    <author>sistema</author>
-  </authors>
-  <commentList>
-    <comment ref="I1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Fórmula: tela+insumos+confección+lavandería</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Fórmula: precio_venta - costo_total</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Fórmula: margen_cop / precio_venta</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Lo llena el sistema al autorizar.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="187">
   <si>
     <t xml:space="preserve">MALE'DENIM OS — Plantilla de Producción (Fase 1)</t>
   </si>
   <si>
-    <t xml:space="preserve">Las hojas están conectadas con fórmulas para mostrar la mecánica del módulo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1) Órdenes de Despacho</t>
+    <t xml:space="preserve">Hojas conectadas con fórmulas para mostrar la mecánica del módulo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Órdenes de Ingreso</t>
   </si>
   <si>
     <t xml:space="preserve">Transcribe la hoja de la textilera, un renglón por rollo. Columnas grises (código/barcode) las genera el sistema.</t>
@@ -156,25 +99,31 @@
     <t xml:space="preserve">2) Inventario</t>
   </si>
   <si>
-    <t xml:space="preserve">Se arma SOLO: unifica por nombre de tela, cuenta rollos y muestra metros disponibles (recibidos − cortados). Tiene un desplegable para ver una tela y su nº de rollos.</t>
+    <t xml:space="preserve">Se arma solo: unifica por nombre de tela, cuenta rollos y muestra metros disponibles (recibidos − cortados). Desplegable para ver una tela.</t>
   </si>
   <si>
     <t xml:space="preserve">3) Cortes</t>
   </si>
   <si>
-    <t xml:space="preserve">Al mandar a cortar eliges la tela POR NOMBRE (desplegable) y los metros; el Inventario se descuenta automáticamente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4) Precosteo Referencias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Costeo de cada referencia de prenda. Se autoriza en la app; la firma se escribe de vuelta aquí.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5) Orden de Corte (formato)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El documento-formato que da luz verde al cortador (referencia, tela por nombre, rollos, indicaciones).</t>
+    <t xml:space="preserve">Eliges la tela POR NOMBRE (desplegable) y los metros; el Inventario se descuenta solo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4) Precosteo (formato)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espejo de tu formato 14500-1: líneas por categoría con IVA, costo total y precio sugerido. Al firmar se archiva en Histórico y se limpia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5) Histórico Precosteo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Donde quedan archivados los precosteos firmados (lo llena el botón Guardar y firmar).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6) Orden de Corte (formato)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documento que da luz verde al cortador.</t>
   </si>
   <si>
     <t xml:space="preserve">Colores</t>
@@ -195,16 +144,13 @@
     <t xml:space="preserve">Texto azul</t>
   </si>
   <si>
-    <t xml:space="preserve">Ejemplos — bórralos antes de usar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Importante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• En la app real el descuento es transaccional por rollo; aquí se demuestra con fórmulas por nombre de tela.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Si la textilera solo da el total (ej. Megatex), registra un renglón con el total.</t>
+    <t xml:space="preserve">Ejemplos — bórralos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guardar y limpiar (reset a 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En Google Sheets se activa con el script Apps Script adjunto: archiva el formato en Histórico y deja los campos en 0. En el módulo es automático.</t>
   </si>
   <si>
     <t xml:space="preserve">textilera</t>
@@ -390,73 +336,217 @@
     <t xml:space="preserve">2026-06-26</t>
   </si>
   <si>
-    <t xml:space="preserve">REF-501</t>
+    <t xml:space="preserve">REF 14500-1</t>
   </si>
   <si>
     <t xml:space="preserve">Cortador 1</t>
   </si>
   <si>
-    <t xml:space="preserve">codigo_referencia</t>
+    <t xml:space="preserve">PRECOSTEO · MALE'DENIM OS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14500-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOMBRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKINNY OSCURO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOTO (link)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERBENA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSCURO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVA %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CATEGORIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALOR UNITARIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANTIDAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL SIN IVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL CON IVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIRTY JEANS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRECIO TELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRECIO COMPLEMENTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPLEMENTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROCESO EN MP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BORDADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROCESO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONFECCION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSUMO CONFECCION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIERRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARQUILLA TALLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANDERA COLOMBIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAVANDERIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TERMINACION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSUMO EMPAQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CODIGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRETINERA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSTRUCCION LAVADO IMPRESA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMPAQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSUMO TERMINACION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTON 27 L PASTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REMACHE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APLIQUES PROFINTEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENTRETELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GASTOS FIJOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COSTO TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRECIO SUGERIDO DE VENTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo base (sin IVA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margen %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio antes de IVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVA 19%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio final con IVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margen real %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTORIZADO POR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FECHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">▶ Botón 'Guardar y firmar' (Apps Script): archiva en 'Histórico Precosteo' y limpia el formato a 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fecha_firma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref</t>
   </si>
   <si>
     <t xml:space="preserve">nombre</t>
   </si>
   <si>
-    <t xml:space="preserve">consumo_tela_prenda_m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">costo_tela_cop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">detalle_insumos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">costo_insumos_cop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">costo_confeccion_cop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">costo_lavanderia_cop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">costo_total_prenda_cop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">precio_venta_cop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">margen_cop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">margen_pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foto_link_opcional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estado_autorizacion</t>
+    <t xml:space="preserve">tela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">costo_total_sin_iva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">costo_total_con_iva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">precio_sugerido</t>
   </si>
   <si>
     <t xml:space="preserve">autorizado_por</t>
   </si>
   <si>
-    <t xml:space="preserve">fecha_autorizacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jean Slim Indigo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Botón, cremallera #4.5, hilo, marquilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REF-502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jean Recto Negro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Botón, cremallera #5, hilo, etiqueta</t>
+    <t xml:space="preserve">(las filas firmadas se agregan aquí automáticamente)</t>
   </si>
   <si>
     <t xml:space="preserve">ORDEN DE CORTE · MALE'DENIM OS</t>
@@ -559,15 +649,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
     <numFmt numFmtId="167" formatCode="0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
-    <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="0%"/>
+    <numFmt numFmtId="170" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -692,17 +783,40 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF666666"/>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2E5A88"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF2E5A88"/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -716,9 +830,17 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <i val="true"/>
       <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF666666"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF999999"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -747,7 +869,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF8A94A6"/>
-        <bgColor rgb="FF808080"/>
+        <bgColor rgb="FF999999"/>
       </patternFill>
     </fill>
     <fill>
@@ -806,7 +928,9 @@
       <top style="thin">
         <color rgb="FFC8D0DA"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FFC8D0DA"/>
+      </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -817,9 +941,7 @@
       <top style="thin">
         <color rgb="FFC8D0DA"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFC8D0DA"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -848,16 +970,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="49">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -865,7 +991,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -877,19 +1003,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -897,15 +1023,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -913,23 +1039,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -937,31 +1055,103 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -969,11 +1159,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1003,7 +1193,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF1E7A46"/>
       <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF8A94A6"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF6CC"/>
@@ -1035,7 +1225,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666666"/>
-      <rgbColor rgb="FF8A94A6"/>
+      <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF1F3A5F"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1229,127 +1419,125 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="92"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="3" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3"/>
+      <c r="B12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="B13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="3"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="B16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="3"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3"/>
+      <c r="B17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="3"/>
+      <c r="B18" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1370,288 +1558,288 @@
   <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="M1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="O1" s="7" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="7" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7" t="s">
+      <c r="G2" s="8"/>
+      <c r="H2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="I2" s="8"/>
+      <c r="J2" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="M2" s="9" t="n">
+      <c r="L2" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="10" t="n">
         <v>47.9</v>
       </c>
-      <c r="N2" s="8" t="n">
+      <c r="N2" s="9" t="n">
         <v>9800</v>
       </c>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="E3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3" s="9" t="n">
+      <c r="M3" s="10" t="n">
         <v>51.1</v>
       </c>
-      <c r="N3" s="8" t="n">
+      <c r="N3" s="9" t="n">
         <v>9800</v>
       </c>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="I4" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="J4" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="L4" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" s="9" t="n">
+      <c r="K4" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="N4" s="8" t="n">
+      <c r="N4" s="9" t="n">
         <v>12500</v>
       </c>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="E5" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="M5" s="9" t="n">
+      <c r="L5" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="10" t="n">
         <v>80.1</v>
       </c>
-      <c r="N5" s="8" t="n">
+      <c r="N5" s="9" t="n">
         <v>12500</v>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="L6" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="M6" s="9" t="n">
+      <c r="K6" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" s="10" t="n">
         <v>307.7</v>
       </c>
-      <c r="N6" s="8" t="n">
+      <c r="N6" s="9" t="n">
         <v>16000</v>
       </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1679,155 +1867,155 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A1" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="B3" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="14" t="n">
         <f aca="false">IFERROR(VLOOKUP(B3,$A$7:$E$20,2,0),0)</f>
         <v>2</v>
       </c>
-      <c r="E3" s="14" t="str">
+      <c r="E3" s="15" t="str">
         <f aca="false">IFERROR("Disponible: "&amp;TEXT(VLOOKUP(B3,$A$7:$E$20,5,0),"#,##0.0")&amp;" m","")</f>
         <v>Disponible: 69.0 m</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="15" t="s">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="B6" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="C6" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="D6" s="16" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="16" t="n">
-        <f aca="false">IF($A7="","",COUNTIF('Órdenes de Despacho'!$K:$K,$A7))</f>
+      <c r="E6" s="16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="17" t="n">
+        <f aca="false">IF($A7="","",COUNTIF('Órdenes de Ingreso'!$K:$K,$A7))</f>
         <v>2</v>
       </c>
-      <c r="C7" s="17" t="n">
-        <f aca="false">IF($A7="","",SUMIF('Órdenes de Despacho'!$K:$K,$A7,'Órdenes de Despacho'!$M:$M))</f>
+      <c r="C7" s="18" t="n">
+        <f aca="false">IF($A7="","",SUMIF('Órdenes de Ingreso'!$K:$K,$A7,'Órdenes de Ingreso'!$M:$M))</f>
         <v>99</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <f aca="false">IF($A7="","",SUMIF(Cortes!$B:$B,$A7,Cortes!$D:$D))</f>
         <v>30</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <f aca="false">IF($A7="","",$C7-$D7)</f>
         <v>69</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="16" t="n">
-        <f aca="false">IF($A8="","",COUNTIF('Órdenes de Despacho'!$K:$K,$A8))</f>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="17" t="n">
+        <f aca="false">IF($A8="","",COUNTIF('Órdenes de Ingreso'!$K:$K,$A8))</f>
         <v>2</v>
       </c>
-      <c r="C8" s="17" t="n">
-        <f aca="false">IF($A8="","",SUMIF('Órdenes de Despacho'!$K:$K,$A8,'Órdenes de Despacho'!$M:$M))</f>
+      <c r="C8" s="18" t="n">
+        <f aca="false">IF($A8="","",SUMIF('Órdenes de Ingreso'!$K:$K,$A8,'Órdenes de Ingreso'!$M:$M))</f>
         <v>162.1</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <f aca="false">IF($A8="","",SUMIF(Cortes!$B:$B,$A8,Cortes!$D:$D))</f>
         <v>0</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <f aca="false">IF($A8="","",$C8-$D8)</f>
         <v>162.1</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="16" t="n">
-        <f aca="false">IF($A9="","",COUNTIF('Órdenes de Despacho'!$K:$K,$A9))</f>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="17" t="n">
+        <f aca="false">IF($A9="","",COUNTIF('Órdenes de Ingreso'!$K:$K,$A9))</f>
         <v>1</v>
       </c>
-      <c r="C9" s="17" t="n">
-        <f aca="false">IF($A9="","",SUMIF('Órdenes de Despacho'!$K:$K,$A9,'Órdenes de Despacho'!$M:$M))</f>
+      <c r="C9" s="18" t="n">
+        <f aca="false">IF($A9="","",SUMIF('Órdenes de Ingreso'!$K:$K,$A9,'Órdenes de Ingreso'!$M:$M))</f>
         <v>307.7</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <f aca="false">IF($A9="","",SUMIF(Cortes!$B:$B,$A9,Cortes!$D:$D))</f>
         <v>0</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <f aca="false">IF($A9="","",$C9-$D9)</f>
         <v>307.7</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7"/>
-      <c r="B10" s="16" t="str">
-        <f aca="false">IF($A10="","",COUNTIF('Órdenes de Despacho'!$K:$K,$A10))</f>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8"/>
+      <c r="B10" s="17" t="str">
+        <f aca="false">IF($A10="","",COUNTIF('Órdenes de Ingreso'!$K:$K,$A10))</f>
         <v/>
       </c>
-      <c r="C10" s="17" t="str">
-        <f aca="false">IF($A10="","",SUMIF('Órdenes de Despacho'!$K:$K,$A10,'Órdenes de Despacho'!$M:$M))</f>
+      <c r="C10" s="18" t="str">
+        <f aca="false">IF($A10="","",SUMIF('Órdenes de Ingreso'!$K:$K,$A10,'Órdenes de Ingreso'!$M:$M))</f>
         <v/>
       </c>
-      <c r="D10" s="17" t="str">
+      <c r="D10" s="18" t="str">
         <f aca="false">IF($A10="","",SUMIF(Cortes!$B:$B,$A10,Cortes!$D:$D))</f>
         <v/>
       </c>
-      <c r="E10" s="17" t="str">
+      <c r="E10" s="18" t="str">
         <f aca="false">IF($A10="","",$C10-$D10)</f>
         <v/>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7"/>
-      <c r="B11" s="16" t="str">
-        <f aca="false">IF($A11="","",COUNTIF('Órdenes de Despacho'!$K:$K,$A11))</f>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8"/>
+      <c r="B11" s="17" t="str">
+        <f aca="false">IF($A11="","",COUNTIF('Órdenes de Ingreso'!$K:$K,$A11))</f>
         <v/>
       </c>
-      <c r="C11" s="17" t="str">
-        <f aca="false">IF($A11="","",SUMIF('Órdenes de Despacho'!$K:$K,$A11,'Órdenes de Despacho'!$M:$M))</f>
+      <c r="C11" s="18" t="str">
+        <f aca="false">IF($A11="","",SUMIF('Órdenes de Ingreso'!$K:$K,$A11,'Órdenes de Ingreso'!$M:$M))</f>
         <v/>
       </c>
-      <c r="D11" s="17" t="str">
+      <c r="D11" s="18" t="str">
         <f aca="false">IF($A11="","",SUMIF(Cortes!$B:$B,$A11,Cortes!$D:$D))</f>
         <v/>
       </c>
-      <c r="E11" s="17" t="str">
+      <c r="E11" s="18" t="str">
         <f aca="false">IF($A11="","",$C11-$D11)</f>
         <v/>
       </c>
@@ -1860,123 +2048,123 @@
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="A1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D2" s="18" t="n">
-        <v>30</v>
-      </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2001,169 +2189,812 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="B2" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="C2" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="D2" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="E2" s="23"/>
+      <c r="F2" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="G2" s="22"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="B3" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="C3" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="D3" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="F3" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="G3" s="24" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="B5" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="C5" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="D5" s="25" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="E5" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="D2" s="8" t="n">
-        <v>13230</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="F5" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="F2" s="8" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G2" s="8" t="n">
-        <v>14000</v>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="I2" s="19" t="n">
-        <f aca="false">SUM(D2,F2,G2,H2)</f>
-        <v>36530</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>89900</v>
-      </c>
-      <c r="K2" s="19" t="n">
-        <f aca="false">J2-I2</f>
-        <v>53370</v>
-      </c>
-      <c r="L2" s="20" t="n">
-        <f aca="false">IF(J2=0,0,K2/J2)</f>
-        <v>0.593659621802002</v>
-      </c>
-      <c r="M2" s="7"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="G5" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="7" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>16240</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="B6" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="F3" s="8" t="n">
-        <v>3100</v>
-      </c>
-      <c r="G3" s="8" t="n">
-        <v>15000</v>
-      </c>
-      <c r="H3" s="8" t="n">
+      <c r="C6" s="28" t="n">
+        <v>15900</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <f aca="false">ROUND(F6*$G$3,0)</f>
+        <v>3021</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <f aca="false">C6*D6</f>
+        <v>15900</v>
+      </c>
+      <c r="G6" s="30" t="n">
+        <f aca="false">F6+E6</f>
+        <v>18921</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="26"/>
+      <c r="B7" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <f aca="false">ROUND(F7*$G$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <f aca="false">C7*D7</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="30" t="n">
+        <f aca="false">F7+E7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>15900</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <f aca="false">ROUND(F8*$G$3,0)</f>
+        <v>3232</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <f aca="false">C8*D8</f>
+        <v>17013</v>
+      </c>
+      <c r="G8" s="30" t="n">
+        <f aca="false">F8+E8</f>
+        <v>20245</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="26"/>
+      <c r="B9" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>4400</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <f aca="false">ROUND(F9*$G$3,0)</f>
+        <v>125</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <f aca="false">C9*D9</f>
+        <v>660</v>
+      </c>
+      <c r="G9" s="30" t="n">
+        <f aca="false">F9+E9</f>
+        <v>785</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="26"/>
+      <c r="B10" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <f aca="false">ROUND(F10*$G$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <f aca="false">C10*D10</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="30" t="n">
+        <f aca="false">F10+E10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <f aca="false">ROUND(F11*$G$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <f aca="false">C11*D11</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="30" t="n">
+        <f aca="false">F11+E11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="28" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <f aca="false">ROUND(F12*$G$3,0)</f>
+        <v>228</v>
+      </c>
+      <c r="F12" s="30" t="n">
+        <f aca="false">C12*D12</f>
+        <v>1200</v>
+      </c>
+      <c r="G12" s="30" t="n">
+        <f aca="false">F12+E12</f>
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="28" t="n">
+        <v>10700</v>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <f aca="false">ROUND(F13*$G$3,0)</f>
+        <v>2033</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <f aca="false">C13*D13</f>
+        <v>10700</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <f aca="false">F13+E13</f>
+        <v>12733</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="28" t="n">
+        <v>700</v>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <f aca="false">ROUND(F14*$G$3,0)</f>
+        <v>133</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <f aca="false">C14*D14</f>
+        <v>700</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <f aca="false">F14+E14</f>
+        <v>833</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="26"/>
+      <c r="B15" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15" s="28" t="n">
+        <v>87</v>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <f aca="false">ROUND(F15*$G$3,0)</f>
+        <v>17</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <f aca="false">C15*D15</f>
+        <v>87</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <f aca="false">F15+E15</f>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="29" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <f aca="false">ROUND(F16*$G$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="30" t="n">
+        <f aca="false">C16*D16</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="30" t="n">
+        <f aca="false">F16+E16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" s="28" t="n">
         <v>7000</v>
       </c>
-      <c r="I3" s="19" t="n">
-        <f aca="false">SUM(D3,F3,G3,H3)</f>
-        <v>41340</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>99900</v>
-      </c>
-      <c r="K3" s="19" t="n">
-        <f aca="false">J3-I3</f>
-        <v>58560</v>
-      </c>
-      <c r="L3" s="20" t="n">
-        <f aca="false">IF(J3=0,0,K3/J3)</f>
-        <v>0.586186186186186</v>
-      </c>
-      <c r="M3" s="7"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
+      <c r="D17" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <f aca="false">ROUND(F17*$G$3,0)</f>
+        <v>1330</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <f aca="false">C17*D17</f>
+        <v>7000</v>
+      </c>
+      <c r="G17" s="30" t="n">
+        <f aca="false">F17+E17</f>
+        <v>8330</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="28" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D18" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <f aca="false">ROUND(F18*$G$3,0)</f>
+        <v>399</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <f aca="false">C18*D18</f>
+        <v>2100</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <f aca="false">F18+E18</f>
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <f aca="false">ROUND(F19*$G$3,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <f aca="false">C19*D19</f>
+        <v>20</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <f aca="false">F19+E19</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" s="28" t="n">
+        <v>123</v>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <f aca="false">ROUND(F20*$G$3,0)</f>
+        <v>23</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <f aca="false">C20*D20</f>
+        <v>123</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <f aca="false">F20+E20</f>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="30" t="n">
+        <f aca="false">ROUND(F21*$G$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="F21" s="30" t="n">
+        <f aca="false">C21*D21</f>
+        <v>10</v>
+      </c>
+      <c r="G21" s="30" t="n">
+        <f aca="false">F21+E21</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="26"/>
+      <c r="B22" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" s="28" t="n">
+        <v>180</v>
+      </c>
+      <c r="D22" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="30" t="n">
+        <f aca="false">ROUND(F22*$G$3,0)</f>
+        <v>34</v>
+      </c>
+      <c r="F22" s="30" t="n">
+        <f aca="false">C22*D22</f>
+        <v>180</v>
+      </c>
+      <c r="G22" s="30" t="n">
+        <f aca="false">F22+E22</f>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="28" t="n">
+        <v>278</v>
+      </c>
+      <c r="D23" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="30" t="n">
+        <f aca="false">ROUND(F23*$G$3,0)</f>
+        <v>53</v>
+      </c>
+      <c r="F23" s="30" t="n">
+        <f aca="false">C23*D23</f>
+        <v>278</v>
+      </c>
+      <c r="G23" s="30" t="n">
+        <f aca="false">F23+E23</f>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="28" t="n">
+        <v>111</v>
+      </c>
+      <c r="D24" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="30" t="n">
+        <f aca="false">ROUND(F24*$G$3,0)</f>
+        <v>42</v>
+      </c>
+      <c r="F24" s="30" t="n">
+        <f aca="false">C24*D24</f>
+        <v>222</v>
+      </c>
+      <c r="G24" s="30" t="n">
+        <f aca="false">F24+E24</f>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="28" t="n">
+        <v>700</v>
+      </c>
+      <c r="D25" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="30" t="n">
+        <f aca="false">ROUND(F25*$G$3,0)</f>
+        <v>133</v>
+      </c>
+      <c r="F25" s="30" t="n">
+        <f aca="false">C25*D25</f>
+        <v>700</v>
+      </c>
+      <c r="G25" s="30" t="n">
+        <f aca="false">F25+E25</f>
+        <v>833</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="30" t="n">
+        <f aca="false">ROUND(F26*$G$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="30" t="n">
+        <f aca="false">C26*D26</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="30" t="n">
+        <f aca="false">F26+E26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="26"/>
+      <c r="B27" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="30" t="n">
+        <f aca="false">ROUND(F27*$G$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="30" t="n">
+        <f aca="false">C27*D27</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="30" t="n">
+        <f aca="false">F27+E27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="28" t="n">
+        <v>11000</v>
+      </c>
+      <c r="D28" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="30" t="n">
+        <f aca="false">ROUND(F28*$G$3,0)</f>
+        <v>2090</v>
+      </c>
+      <c r="F28" s="30" t="n">
+        <f aca="false">C28*D28</f>
+        <v>11000</v>
+      </c>
+      <c r="G28" s="30" t="n">
+        <f aca="false">F28+E28</f>
+        <v>13090</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="31"/>
+      <c r="B29" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="33" t="n">
+        <f aca="false">SUM(F6:F28)</f>
+        <v>67893</v>
+      </c>
+      <c r="G29" s="33" t="n">
+        <f aca="false">SUM(G6:G28)</f>
+        <v>80792</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="34" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="B32" s="35" t="n">
+        <f aca="false">F29</f>
+        <v>67893</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B34" s="30" t="n">
+        <f aca="false">ROUND($B$32*(1+A34),0)</f>
+        <v>101840</v>
+      </c>
+      <c r="C34" s="30" t="n">
+        <f aca="false">ROUND(B34*$G$3,0)</f>
+        <v>19350</v>
+      </c>
+      <c r="D34" s="36" t="n">
+        <f aca="false">B34+C34</f>
+        <v>121190</v>
+      </c>
+      <c r="E34" s="37" t="n">
+        <f aca="false">IF(B34=0,0,(B34-$B$32)/B34)</f>
+        <v>0.333336606441477</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="24" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="B35" s="30" t="n">
+        <f aca="false">ROUND($B$32*(1+A35),0)</f>
+        <v>112023</v>
+      </c>
+      <c r="C35" s="30" t="n">
+        <f aca="false">ROUND(B35*$G$3,0)</f>
+        <v>21284</v>
+      </c>
+      <c r="D35" s="36" t="n">
+        <f aca="false">B35+C35</f>
+        <v>133307</v>
+      </c>
+      <c r="E35" s="37" t="n">
+        <f aca="false">IF(B35=0,0,(B35-$B$32)/B35)</f>
+        <v>0.393936959374414</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B36" s="30" t="n">
+        <f aca="false">ROUND($B$32*(1+A36),0)</f>
+        <v>122207</v>
+      </c>
+      <c r="C36" s="30" t="n">
+        <f aca="false">ROUND(B36*$G$3,0)</f>
+        <v>23219</v>
+      </c>
+      <c r="D36" s="36" t="n">
+        <f aca="false">B36+C36</f>
+        <v>145426</v>
+      </c>
+      <c r="E36" s="37" t="n">
+        <f aca="false">IF(B36=0,0,(B36-$B$32)/B36)</f>
+        <v>0.444442626036152</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="B38" s="22"/>
+      <c r="C38" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D38" s="22"/>
+      <c r="F38" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="G38" s="22"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="B40" s="38"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
     </row>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A27"/>
+    <mergeCell ref="A40:G40"/>
+  </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="N2:N500" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B38" type="list">
       <formula1>"borrador,autorizada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2175,7 +3006,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2184,256 +3014,319 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="39" t="s">
+        <v>154</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
+      <c r="A1" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="7"/>
+      <c r="A4" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="D5" s="7"/>
+      <c r="A5" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="D5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" s="25" t="n">
+      <c r="A6" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="D6" s="42" t="n">
         <f aca="false">IFERROR(VLOOKUP(B6,Inventario!$A$7:$E$20,5,0),0)</f>
         <v>69</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="D7" s="7"/>
+      <c r="A7" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="D7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="s">
-        <v>116</v>
+      <c r="A9" s="43" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="27" t="s">
+      <c r="A10" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="27" t="s">
-        <v>80</v>
+      <c r="D10" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
+      <c r="A11" s="45"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
+      <c r="A12" s="45"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
+      <c r="A13" s="45"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
+      <c r="A14" s="45"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="26" t="s">
-        <v>117</v>
+      <c r="A16" s="43" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="D17" s="7"/>
+      <c r="A17" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="D18" s="7"/>
+      <c r="A18" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="D18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="D19" s="7"/>
+      <c r="A19" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="B19" s="8"/>
+      <c r="C19" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="D19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="D20" s="7"/>
+      <c r="A20" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="B20" s="8"/>
+      <c r="C20" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="26" t="s">
-        <v>126</v>
+      <c r="A22" s="43" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="E23" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F23" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="G23" s="27" t="s">
-        <v>133</v>
+      <c r="A23" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="B23" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="C23" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="E23" s="44" t="s">
+        <v>180</v>
+      </c>
+      <c r="F23" s="44" t="s">
+        <v>181</v>
+      </c>
+      <c r="G23" s="44" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="29"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
+      <c r="A24" s="46"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="26" t="s">
-        <v>134</v>
+      <c r="A26" s="43" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
+      <c r="A27" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="30"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
+      <c r="A28" s="47"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="30"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
+      <c r="A29" s="47"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="E31" s="7"/>
+      <c r="A31" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="B31" s="48"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="E31" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/sheets/Produccion_Sheet_Plantilla.xlsx
+++ b/sheets/Produccion_Sheet_Plantilla.xlsx
@@ -486,7 +486,7 @@
     <t xml:space="preserve">COSTO TOTAL</t>
   </si>
   <si>
-    <t xml:space="preserve">PRECIO SUGERIDO DE VENTA</t>
+    <t xml:space="preserve">PRECIO SUGERIDO DE VENTA (CON IVA)</t>
   </si>
   <si>
     <t xml:space="preserve">Costo base (sin IVA)</t>
@@ -495,13 +495,13 @@
     <t xml:space="preserve">Margen %</t>
   </si>
   <si>
+    <t xml:space="preserve">PRECIO VENTA (con IVA)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Precio antes de IVA</t>
   </si>
   <si>
     <t xml:space="preserve">IVA 19%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Precio final con IVA</t>
   </si>
   <si>
     <t xml:space="preserve">Margen real %</t>
@@ -658,7 +658,7 @@
     <numFmt numFmtId="169" formatCode="0%"/>
     <numFmt numFmtId="170" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -830,6 +830,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <i val="true"/>
       <sz val="9"/>
       <color rgb="FF666666"/>
@@ -970,7 +977,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="47">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1059,15 +1066,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1079,59 +1082,59 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1151,7 +1154,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1161,10 +1164,6 @@
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2192,13 +2191,13 @@
   <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2212,773 +2211,801 @@
       <c r="F1" s="20"/>
       <c r="G1" s="20"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="8" t="s">
         <v>88</v>
       </c>
       <c r="C2" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="E2" s="23"/>
+      <c r="E2" s="22"/>
       <c r="F2" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="G2" s="22"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G2" s="8"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="8" t="s">
         <v>93</v>
       </c>
       <c r="C3" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="8" t="s">
         <v>95</v>
       </c>
       <c r="F3" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="24" t="n">
+      <c r="G3" s="23" t="n">
         <v>0.19</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="24" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="9" t="n">
         <v>15900</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="27" t="n">
         <f aca="false">ROUND(F6*$G$3,0)</f>
         <v>3021</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="27" t="n">
         <f aca="false">C6*D6</f>
         <v>15900</v>
       </c>
-      <c r="G6" s="30" t="n">
+      <c r="G6" s="27" t="n">
         <f aca="false">F6+E6</f>
         <v>18921</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26"/>
-      <c r="B7" s="27" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="25"/>
+      <c r="B7" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="27" t="n">
         <f aca="false">ROUND(F7*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="30" t="n">
+      <c r="F7" s="27" t="n">
         <f aca="false">C7*D7</f>
         <v>0</v>
       </c>
-      <c r="G7" s="30" t="n">
+      <c r="G7" s="27" t="n">
         <f aca="false">F7+E7</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="9" t="n">
         <v>15900</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="10" t="n">
         <v>1.07</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="27" t="n">
         <f aca="false">ROUND(F8*$G$3,0)</f>
         <v>3232</v>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F8" s="27" t="n">
         <f aca="false">C8*D8</f>
         <v>17013</v>
       </c>
-      <c r="G8" s="30" t="n">
+      <c r="G8" s="27" t="n">
         <f aca="false">F8+E8</f>
         <v>20245</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26"/>
-      <c r="B9" s="27" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="25"/>
+      <c r="B9" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="9" t="n">
         <v>4400</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="27" t="n">
         <f aca="false">ROUND(F9*$G$3,0)</f>
         <v>125</v>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F9" s="27" t="n">
         <f aca="false">C9*D9</f>
         <v>660</v>
       </c>
-      <c r="G9" s="30" t="n">
+      <c r="G9" s="27" t="n">
         <f aca="false">F9+E9</f>
         <v>785</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26"/>
-      <c r="B10" s="27" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="25"/>
+      <c r="B10" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="27" t="n">
         <f aca="false">ROUND(F10*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="30" t="n">
+      <c r="F10" s="27" t="n">
         <f aca="false">C10*D10</f>
         <v>0</v>
       </c>
-      <c r="G10" s="30" t="n">
+      <c r="G10" s="27" t="n">
         <f aca="false">F10+E10</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="27" t="n">
         <f aca="false">ROUND(F11*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="30" t="n">
+      <c r="F11" s="27" t="n">
         <f aca="false">C11*D11</f>
         <v>0</v>
       </c>
-      <c r="G11" s="30" t="n">
+      <c r="G11" s="27" t="n">
         <f aca="false">F11+E11</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="9" t="n">
         <v>1200</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="30" t="n">
+      <c r="E12" s="27" t="n">
         <f aca="false">ROUND(F12*$G$3,0)</f>
         <v>228</v>
       </c>
-      <c r="F12" s="30" t="n">
+      <c r="F12" s="27" t="n">
         <f aca="false">C12*D12</f>
         <v>1200</v>
       </c>
-      <c r="G12" s="30" t="n">
+      <c r="G12" s="27" t="n">
         <f aca="false">F12+E12</f>
         <v>1428</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="C13" s="28" t="n">
+      <c r="C13" s="9" t="n">
         <v>10700</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="30" t="n">
+      <c r="E13" s="27" t="n">
         <f aca="false">ROUND(F13*$G$3,0)</f>
         <v>2033</v>
       </c>
-      <c r="F13" s="30" t="n">
+      <c r="F13" s="27" t="n">
         <f aca="false">C13*D13</f>
         <v>10700</v>
       </c>
-      <c r="G13" s="30" t="n">
+      <c r="G13" s="27" t="n">
         <f aca="false">F13+E13</f>
         <v>12733</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="28" t="n">
+      <c r="C14" s="9" t="n">
         <v>700</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="30" t="n">
+      <c r="E14" s="27" t="n">
         <f aca="false">ROUND(F14*$G$3,0)</f>
         <v>133</v>
       </c>
-      <c r="F14" s="30" t="n">
+      <c r="F14" s="27" t="n">
         <f aca="false">C14*D14</f>
         <v>700</v>
       </c>
-      <c r="G14" s="30" t="n">
+      <c r="G14" s="27" t="n">
         <f aca="false">F14+E14</f>
         <v>833</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="25"/>
+      <c r="B15" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="28" t="n">
+      <c r="C15" s="9" t="n">
         <v>87</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="30" t="n">
+      <c r="E15" s="27" t="n">
         <f aca="false">ROUND(F15*$G$3,0)</f>
         <v>17</v>
       </c>
-      <c r="F15" s="30" t="n">
+      <c r="F15" s="27" t="n">
         <f aca="false">C15*D15</f>
         <v>87</v>
       </c>
-      <c r="G15" s="30" t="n">
+      <c r="G15" s="27" t="n">
         <f aca="false">F15+E15</f>
         <v>104</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="28" t="n">
+      <c r="C16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="10" t="n">
         <v>0.07</v>
       </c>
-      <c r="E16" s="30" t="n">
+      <c r="E16" s="27" t="n">
         <f aca="false">ROUND(F16*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="30" t="n">
+      <c r="F16" s="27" t="n">
         <f aca="false">C16*D16</f>
         <v>0</v>
       </c>
-      <c r="G16" s="30" t="n">
+      <c r="G16" s="27" t="n">
         <f aca="false">F16+E16</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="C17" s="28" t="n">
+      <c r="C17" s="9" t="n">
         <v>7000</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="30" t="n">
+      <c r="E17" s="27" t="n">
         <f aca="false">ROUND(F17*$G$3,0)</f>
         <v>1330</v>
       </c>
-      <c r="F17" s="30" t="n">
+      <c r="F17" s="27" t="n">
         <f aca="false">C17*D17</f>
         <v>7000</v>
       </c>
-      <c r="G17" s="30" t="n">
+      <c r="G17" s="27" t="n">
         <f aca="false">F17+E17</f>
         <v>8330</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="26"/>
-      <c r="B18" s="27" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="25"/>
+      <c r="B18" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="C18" s="28" t="n">
+      <c r="C18" s="9" t="n">
         <v>2100</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="30" t="n">
+      <c r="E18" s="27" t="n">
         <f aca="false">ROUND(F18*$G$3,0)</f>
         <v>399</v>
       </c>
-      <c r="F18" s="30" t="n">
+      <c r="F18" s="27" t="n">
         <f aca="false">C18*D18</f>
         <v>2100</v>
       </c>
-      <c r="G18" s="30" t="n">
+      <c r="G18" s="27" t="n">
         <f aca="false">F18+E18</f>
         <v>2499</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="C19" s="28" t="n">
+      <c r="C19" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="30" t="n">
+      <c r="E19" s="27" t="n">
         <f aca="false">ROUND(F19*$G$3,0)</f>
         <v>4</v>
       </c>
-      <c r="F19" s="30" t="n">
+      <c r="F19" s="27" t="n">
         <f aca="false">C19*D19</f>
         <v>20</v>
       </c>
-      <c r="G19" s="30" t="n">
+      <c r="G19" s="27" t="n">
         <f aca="false">F19+E19</f>
         <v>24</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="25"/>
+      <c r="B20" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="28" t="n">
+      <c r="C20" s="9" t="n">
         <v>123</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="30" t="n">
+      <c r="E20" s="27" t="n">
         <f aca="false">ROUND(F20*$G$3,0)</f>
         <v>23</v>
       </c>
-      <c r="F20" s="30" t="n">
+      <c r="F20" s="27" t="n">
         <f aca="false">C20*D20</f>
         <v>123</v>
       </c>
-      <c r="G20" s="30" t="n">
+      <c r="G20" s="27" t="n">
         <f aca="false">F20+E20</f>
         <v>146</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="25"/>
+      <c r="B21" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="28" t="n">
+      <c r="C21" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="30" t="n">
+      <c r="E21" s="27" t="n">
         <f aca="false">ROUND(F21*$G$3,0)</f>
         <v>2</v>
       </c>
-      <c r="F21" s="30" t="n">
+      <c r="F21" s="27" t="n">
         <f aca="false">C21*D21</f>
         <v>10</v>
       </c>
-      <c r="G21" s="30" t="n">
+      <c r="G21" s="27" t="n">
         <f aca="false">F21+E21</f>
         <v>12</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="25"/>
+      <c r="B22" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="C22" s="28" t="n">
+      <c r="C22" s="9" t="n">
         <v>180</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="30" t="n">
+      <c r="E22" s="27" t="n">
         <f aca="false">ROUND(F22*$G$3,0)</f>
         <v>34</v>
       </c>
-      <c r="F22" s="30" t="n">
+      <c r="F22" s="27" t="n">
         <f aca="false">C22*D22</f>
         <v>180</v>
       </c>
-      <c r="G22" s="30" t="n">
+      <c r="G22" s="27" t="n">
         <f aca="false">F22+E22</f>
         <v>214</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="28" t="n">
+      <c r="C23" s="9" t="n">
         <v>278</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="30" t="n">
+      <c r="E23" s="27" t="n">
         <f aca="false">ROUND(F23*$G$3,0)</f>
         <v>53</v>
       </c>
-      <c r="F23" s="30" t="n">
+      <c r="F23" s="27" t="n">
         <f aca="false">C23*D23</f>
         <v>278</v>
       </c>
-      <c r="G23" s="30" t="n">
+      <c r="G23" s="27" t="n">
         <f aca="false">F23+E23</f>
         <v>331</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="25"/>
+      <c r="B24" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="C24" s="28" t="n">
+      <c r="C24" s="9" t="n">
         <v>111</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="30" t="n">
+      <c r="E24" s="27" t="n">
         <f aca="false">ROUND(F24*$G$3,0)</f>
         <v>42</v>
       </c>
-      <c r="F24" s="30" t="n">
+      <c r="F24" s="27" t="n">
         <f aca="false">C24*D24</f>
         <v>222</v>
       </c>
-      <c r="G24" s="30" t="n">
+      <c r="G24" s="27" t="n">
         <f aca="false">F24+E24</f>
         <v>264</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26"/>
-      <c r="B25" s="27" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="25"/>
+      <c r="B25" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="C25" s="28" t="n">
+      <c r="C25" s="9" t="n">
         <v>700</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="30" t="n">
+      <c r="E25" s="27" t="n">
         <f aca="false">ROUND(F25*$G$3,0)</f>
         <v>133</v>
       </c>
-      <c r="F25" s="30" t="n">
+      <c r="F25" s="27" t="n">
         <f aca="false">C25*D25</f>
         <v>700</v>
       </c>
-      <c r="G25" s="30" t="n">
+      <c r="G25" s="27" t="n">
         <f aca="false">F25+E25</f>
         <v>833</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="25"/>
+      <c r="B26" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="C26" s="28" t="n">
+      <c r="C26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="30" t="n">
+      <c r="E26" s="27" t="n">
         <f aca="false">ROUND(F26*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F26" s="30" t="n">
+      <c r="F26" s="27" t="n">
         <f aca="false">C26*D26</f>
         <v>0</v>
       </c>
-      <c r="G26" s="30" t="n">
+      <c r="G26" s="27" t="n">
         <f aca="false">F26+E26</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="26"/>
-      <c r="B27" s="27" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="25"/>
+      <c r="B27" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="C27" s="28" t="n">
+      <c r="C27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="30" t="n">
+      <c r="E27" s="27" t="n">
         <f aca="false">ROUND(F27*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="30" t="n">
+      <c r="F27" s="27" t="n">
         <f aca="false">C27*D27</f>
         <v>0</v>
       </c>
-      <c r="G27" s="30" t="n">
+      <c r="G27" s="27" t="n">
         <f aca="false">F27+E27</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="26" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="C28" s="28" t="n">
+      <c r="C28" s="9" t="n">
         <v>11000</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="30" t="n">
+      <c r="E28" s="27" t="n">
         <f aca="false">ROUND(F28*$G$3,0)</f>
         <v>2090</v>
       </c>
-      <c r="F28" s="30" t="n">
+      <c r="F28" s="27" t="n">
         <f aca="false">C28*D28</f>
         <v>11000</v>
       </c>
-      <c r="G28" s="30" t="n">
+      <c r="G28" s="27" t="n">
         <f aca="false">F28+E28</f>
         <v>13090</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="31"/>
-      <c r="B29" s="32" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="28"/>
+      <c r="B29" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="33" t="n">
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="30" t="n">
         <f aca="false">SUM(F6:F28)</f>
         <v>67893</v>
       </c>
-      <c r="G29" s="33" t="n">
+      <c r="G29" s="30" t="n">
         <f aca="false">SUM(G6:G28)</f>
         <v>80792</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="34" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="31" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="32"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B32" s="35" t="n">
+      <c r="B32" s="33" t="n">
         <f aca="false">F29</f>
         <v>67893</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="25" t="s">
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+    </row>
+    <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="D33" s="25" t="s">
+      <c r="D33" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="E33" s="25" t="s">
+      <c r="E33" s="24" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="24" t="n">
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="23" t="n">
         <v>0.5</v>
       </c>
-      <c r="B34" s="30" t="n">
-        <f aca="false">ROUND($B$32*(1+A34),0)</f>
-        <v>101840</v>
-      </c>
-      <c r="C34" s="30" t="n">
-        <f aca="false">ROUND(B34*$G$3,0)</f>
+      <c r="B34" s="34" t="n">
+        <f aca="false">ROUND($B$32*(1+A34)*(1+$G$3),0)</f>
+        <v>121189</v>
+      </c>
+      <c r="C34" s="35" t="n">
+        <f aca="false">ROUND(B34/(1+$G$3),0)</f>
+        <v>101839</v>
+      </c>
+      <c r="D34" s="34" t="n">
+        <f aca="false">B34-C34</f>
         <v>19350</v>
       </c>
-      <c r="D34" s="36" t="n">
-        <f aca="false">B34+C34</f>
-        <v>121190</v>
-      </c>
-      <c r="E34" s="37" t="n">
-        <f aca="false">IF(B34=0,0,(B34-$B$32)/B34)</f>
-        <v>0.333336606441477</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="24" t="n">
+      <c r="E34" s="36" t="n">
+        <f aca="false">IF(C34=0,0,(C34-$B$32)/C34)</f>
+        <v>0.33333006019305</v>
+      </c>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="23" t="n">
         <v>0.65</v>
       </c>
-      <c r="B35" s="30" t="n">
-        <f aca="false">ROUND($B$32*(1+A35),0)</f>
-        <v>112023</v>
-      </c>
-      <c r="C35" s="30" t="n">
-        <f aca="false">ROUND(B35*$G$3,0)</f>
+      <c r="B35" s="34" t="n">
+        <f aca="false">ROUND($B$32*(1+A35)*(1+$G$3),0)</f>
+        <v>133308</v>
+      </c>
+      <c r="C35" s="35" t="n">
+        <f aca="false">ROUND(B35/(1+$G$3),0)</f>
+        <v>112024</v>
+      </c>
+      <c r="D35" s="34" t="n">
+        <f aca="false">B35-C35</f>
         <v>21284</v>
       </c>
-      <c r="D35" s="36" t="n">
-        <f aca="false">B35+C35</f>
-        <v>133307</v>
-      </c>
-      <c r="E35" s="37" t="n">
-        <f aca="false">IF(B35=0,0,(B35-$B$32)/B35)</f>
-        <v>0.393936959374414</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="24" t="n">
+      <c r="E35" s="36" t="n">
+        <f aca="false">IF(C35=0,0,(C35-$B$32)/C35)</f>
+        <v>0.393942369492252</v>
+      </c>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="23" t="n">
         <v>0.8</v>
       </c>
-      <c r="B36" s="30" t="n">
-        <f aca="false">ROUND($B$32*(1+A36),0)</f>
-        <v>122207</v>
-      </c>
-      <c r="C36" s="30" t="n">
-        <f aca="false">ROUND(B36*$G$3,0)</f>
+      <c r="B36" s="34" t="n">
+        <f aca="false">ROUND($B$32*(1+A36)*(1+$G$3),0)</f>
+        <v>145427</v>
+      </c>
+      <c r="C36" s="35" t="n">
+        <f aca="false">ROUND(B36/(1+$G$3),0)</f>
+        <v>122208</v>
+      </c>
+      <c r="D36" s="34" t="n">
+        <f aca="false">B36-C36</f>
         <v>23219</v>
       </c>
-      <c r="D36" s="36" t="n">
-        <f aca="false">B36+C36</f>
-        <v>145426</v>
-      </c>
-      <c r="E36" s="37" t="n">
-        <f aca="false">IF(B36=0,0,(B36-$B$32)/B36)</f>
-        <v>0.444442626036152</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E36" s="36" t="n">
+        <f aca="false">IF(C36=0,0,(C36-$B$32)/C36)</f>
+        <v>0.444447172034564</v>
+      </c>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="32"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+    </row>
+    <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="B38" s="22"/>
+      <c r="B38" s="8"/>
       <c r="C38" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="D38" s="22"/>
+      <c r="D38" s="8"/>
       <c r="F38" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="G38" s="22"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="38" t="s">
+      <c r="G38" s="8"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="B40" s="38"/>
-      <c r="C40" s="38"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="38"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="38"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3057,7 +3084,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="38" t="s">
         <v>154</v>
       </c>
     </row>
@@ -3095,14 +3122,14 @@
       <c r="F1" s="20"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
@@ -3128,13 +3155,13 @@
       <c r="A6" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="40" t="s">
         <v>47</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="D6" s="42" t="n">
+      <c r="D6" s="41" t="n">
         <f aca="false">IFERROR(VLOOKUP(B6,Inventario!$A$7:$E$20,5,0),0)</f>
         <v>69</v>
       </c>
@@ -3151,58 +3178,58 @@
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="42" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="43" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="45"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
+      <c r="A11" s="44"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="45"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
+      <c r="A12" s="44"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="45"/>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
+      <c r="A14" s="44"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="42" t="s">
         <v>166</v>
       </c>
     </row>
@@ -3248,81 +3275,81 @@
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="42" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="44" t="s">
+      <c r="A23" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="B23" s="44" t="s">
+      <c r="B23" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="43" t="s">
         <v>178</v>
       </c>
-      <c r="D23" s="44" t="s">
+      <c r="D23" s="43" t="s">
         <v>179</v>
       </c>
-      <c r="E23" s="44" t="s">
+      <c r="E23" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="F23" s="44" t="s">
+      <c r="F23" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="G23" s="44" t="s">
+      <c r="G23" s="43" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="46"/>
-      <c r="B24" s="46"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
+      <c r="A24" s="45"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="43" t="s">
+      <c r="A26" s="42" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="46" t="s">
         <v>184</v>
       </c>
-      <c r="B27" s="47"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="47"/>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
+      <c r="A28" s="46"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="47"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
+      <c r="A29" s="46"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="B31" s="48"/>
-      <c r="C31" s="48"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
       <c r="D31" s="21" t="s">
         <v>186</v>
       </c>

--- a/sheets/Produccion_Sheet_Plantilla.xlsx
+++ b/sheets/Produccion_Sheet_Plantilla.xlsx
@@ -82,9 +82,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="187">
-  <si>
-    <t xml:space="preserve">MALE'DENIM OS — Plantilla de Producción (Fase 1)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="183">
+  <si>
+    <t xml:space="preserve">Plantilla de Producción — Fase 1</t>
   </si>
   <si>
     <t xml:space="preserve">Hojas conectadas con fórmulas para mostrar la mecánica del módulo.</t>
@@ -93,7 +93,7 @@
     <t xml:space="preserve">1) Órdenes de Ingreso</t>
   </si>
   <si>
-    <t xml:space="preserve">Transcribe la hoja de la textilera, un renglón por rollo. Columnas grises (código/barcode) las genera el sistema.</t>
+    <t xml:space="preserve">Transcribe la hoja de la textilera, un renglón por rollo. Columnas en azul acero (código/barcode) las genera el sistema.</t>
   </si>
   <si>
     <t xml:space="preserve">2) Inventario</t>
@@ -111,13 +111,13 @@
     <t xml:space="preserve">4) Precosteo (formato)</t>
   </si>
   <si>
-    <t xml:space="preserve">Espejo de tu formato 14500-1: líneas por categoría con IVA, costo total y precio sugerido. Al firmar se archiva en Histórico y se limpia.</t>
+    <t xml:space="preserve">Espejo de tu formato: líneas por categoría con IVA, costo total y precio sugerido (con IVA). Al firmar se archiva en Histórico y se limpia.</t>
   </si>
   <si>
     <t xml:space="preserve">5) Histórico Precosteo</t>
   </si>
   <si>
-    <t xml:space="preserve">Donde quedan archivados los precosteos firmados (lo llena el botón Guardar y firmar).</t>
+    <t xml:space="preserve">Donde quedan archivados los precosteos firmados.</t>
   </si>
   <si>
     <t xml:space="preserve">6) Orden de Corte (formato)</t>
@@ -126,31 +126,19 @@
     <t xml:space="preserve">Documento que da luz verde al cortador.</t>
   </si>
   <si>
+    <t xml:space="preserve">Marca</t>
+  </si>
+  <si>
     <t xml:space="preserve">Colores</t>
   </si>
   <si>
-    <t xml:space="preserve">Encabezado azul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo llenas tú.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Encabezado gris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo llena el sistema.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Texto azul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ejemplos — bórralos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guardar y limpiar (reset a 0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En Google Sheets se activa con el script Apps Script adjunto: archiva el formato en Histórico y deja los campos en 0. En el módulo es automático.</t>
+    <t xml:space="preserve">DEEP INK #213033 · GRAPHITE #606060 · STEEL BLUE #87A6B8 · SOFT CONCRETE #E1E1DF · acentos cream/teal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipografía</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montserrat (equivalente de Gotham). Texto editable en azul #0C457A.</t>
   </si>
   <si>
     <t xml:space="preserve">textilera</t>
@@ -297,7 +285,7 @@
     <t xml:space="preserve">BRUSELAS INDIGO 9.8oz</t>
   </si>
   <si>
-    <t xml:space="preserve">INVENTARIO DE TELA — unificado por nombre</t>
+    <t xml:space="preserve">          INVENTARIO DE TELA — unificado por nombre</t>
   </si>
   <si>
     <t xml:space="preserve">Ver tela:</t>
@@ -342,7 +330,7 @@
     <t xml:space="preserve">Cortador 1</t>
   </si>
   <si>
-    <t xml:space="preserve">PRECOSTEO · MALE'DENIM OS</t>
+    <t xml:space="preserve">          PRECOSTEO</t>
   </si>
   <si>
     <t xml:space="preserve">REF</t>
@@ -540,7 +528,7 @@
     <t xml:space="preserve">costo_total_con_iva</t>
   </si>
   <si>
-    <t xml:space="preserve">precio_sugerido</t>
+    <t xml:space="preserve">precio_venta_con_iva</t>
   </si>
   <si>
     <t xml:space="preserve">autorizado_por</t>
@@ -549,7 +537,7 @@
     <t xml:space="preserve">(las filas firmadas se agregan aquí automáticamente)</t>
   </si>
   <si>
-    <t xml:space="preserve">ORDEN DE CORTE · MALE'DENIM OS</t>
+    <t xml:space="preserve">          ORDEN DE CORTE</t>
   </si>
   <si>
     <t xml:space="preserve">Documento que autoriza al cortador a iniciar (luz verde)</t>
@@ -658,7 +646,7 @@
     <numFmt numFmtId="169" formatCode="0%"/>
     <numFmt numFmtId="170" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -683,30 +671,24 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FF1F3A5F"/>
-      <name val="Arial"/>
+      <sz val="15"/>
+      <color rgb="FF213033"/>
+      <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
+      <color rgb="FF213033"/>
+      <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF2E5A88"/>
-      <name val="Arial"/>
+      <color rgb="FF213033"/>
+      <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -714,21 +696,21 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
+      <color rgb="FF0C457A"/>
+      <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <color rgb="FF213033"/>
+      <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -739,54 +721,48 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="15"/>
+      <sz val="16"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
+      <color rgb="FF0C457A"/>
+      <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="12"/>
-      <color rgb="FF1E7A46"/>
-      <name val="Arial"/>
+      <color rgb="FF036A73"/>
+      <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF1E7A46"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <color rgb="FF036A73"/>
+      <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF2E5A88"/>
-      <name val="Arial"/>
+      <color rgb="FF036A73"/>
+      <name val="Montserrat"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF213033"/>
+      <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -794,22 +770,22 @@
       <b val="true"/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="9"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
+      <color rgb="FF606060"/>
+      <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
+      <color rgb="FF213033"/>
+      <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -817,30 +793,15 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF1F3A5F"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
+      <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
       <sz val="9"/>
-      <color rgb="FF666666"/>
-      <name val="Arial"/>
+      <color rgb="FF606060"/>
+      <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -848,14 +809,14 @@
       <i val="true"/>
       <sz val="9"/>
       <color rgb="FF999999"/>
-      <name val="Arial"/>
+      <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
+      <color rgb="FF0C457A"/>
+      <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -869,38 +830,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3A5F"/>
-        <bgColor rgb="FF333333"/>
+        <fgColor rgb="FF213033"/>
+        <bgColor rgb="FF333300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8A94A6"/>
+        <fgColor rgb="FF87A6B8"/>
         <bgColor rgb="FF999999"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF2F7"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFF2F1EF"/>
+        <bgColor rgb="FFF1EAD8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF6CC"/>
-        <bgColor rgb="FFEEF2F7"/>
+        <fgColor rgb="FFF1EAD8"/>
+        <bgColor rgb="FFF2F1EF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2E5A88"/>
-        <bgColor rgb="FF1F3A5F"/>
+        <fgColor rgb="FF606060"/>
+        <bgColor rgb="FF808080"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDCE5EF"/>
-        <bgColor rgb="FFEEF2F7"/>
+        <fgColor rgb="FFE1E1DF"/>
+        <bgColor rgb="FFF1EAD8"/>
       </patternFill>
     </fill>
   </fills>
@@ -977,192 +938,180 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1190,13 +1139,13 @@
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF1E7A46"/>
+      <rgbColor rgb="FF036A73"/>
       <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF8A94A6"/>
-      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF87A6B8"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF6CC"/>
-      <rgbColor rgb="FFEEF2F7"/>
+      <rgbColor rgb="FFF2F1EF"/>
+      <rgbColor rgb="FFE1E1DF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -1210,8 +1159,8 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFDCE5EF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF1EAD8"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -1223,19 +1172,148 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666666"/>
+      <rgbColor rgb="FF606060"/>
       <rgbColor rgb="FF999999"/>
-      <rgbColor rgb="FF1F3A5F"/>
+      <rgbColor rgb="FF0C457A"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF2E5A88"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF213033"/>
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1638000</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>171360</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1638000" cy="552240"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>676080</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>228240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="676080" cy="228240"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>732960</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>247320</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="732960" cy="247320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1418,124 +1496,104 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A4:B18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="92"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="4" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2"/>
+      <c r="B6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="B7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="B16" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3"/>
-      <c r="B17" s="4"/>
-    </row>
-    <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1546,6 +1604,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1557,288 +1616,288 @@
   <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="6" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="C2" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="G2" s="7"/>
+      <c r="H2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="I2" s="7"/>
+      <c r="J2" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="K2" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8" t="s">
+      <c r="M2" s="9" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="N2" s="8" t="n">
+        <v>9800</v>
+      </c>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8" t="s">
+      <c r="G3" s="7"/>
+      <c r="H3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3" s="9" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="N3" s="8" t="n">
+        <v>9800</v>
+      </c>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="10" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="N2" s="9" t="n">
-        <v>9800</v>
-      </c>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8" t="s">
+      <c r="E4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>12500</v>
+      </c>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="M3" s="10" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="N3" s="9" t="n">
-        <v>9800</v>
-      </c>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="D5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="8" t="s">
+      <c r="F5" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="I5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="J5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="K5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="J4" s="8" t="s">
+      <c r="L5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>80.1</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>12500</v>
+      </c>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L4" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="M4" s="10" t="n">
-        <v>82</v>
-      </c>
-      <c r="N4" s="9" t="n">
-        <v>12500</v>
-      </c>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="M5" s="10" t="n">
-        <v>80.1</v>
-      </c>
-      <c r="N5" s="9" t="n">
-        <v>12500</v>
-      </c>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="K6" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="M6" s="10" t="n">
+      <c r="L6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="9" t="n">
         <v>307.7</v>
       </c>
-      <c r="N6" s="9" t="n">
+      <c r="N6" s="8" t="n">
         <v>16000</v>
       </c>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1866,71 +1925,71 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="14" t="n">
+    <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="13" t="n">
         <f aca="false">IFERROR(VLOOKUP(B3,$A$7:$E$20,2,0),0)</f>
         <v>2</v>
       </c>
-      <c r="E3" s="15" t="str">
+      <c r="E3" s="14" t="str">
         <f aca="false">IFERROR("Disponible: "&amp;TEXT(VLOOKUP(B3,$A$7:$E$20,5,0),"#,##0.0")&amp;" m","")</f>
         <v>Disponible: 69.0 m</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="17" t="n">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="16" t="n">
         <f aca="false">IF($A7="","",COUNTIF('Órdenes de Ingreso'!$K:$K,$A7))</f>
         <v>2</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="17" t="n">
         <f aca="false">IF($A7="","",SUMIF('Órdenes de Ingreso'!$K:$K,$A7,'Órdenes de Ingreso'!$M:$M))</f>
         <v>99</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="17" t="n">
         <f aca="false">IF($A7="","",SUMIF(Cortes!$B:$B,$A7,Cortes!$D:$D))</f>
         <v>30</v>
       </c>
@@ -1939,19 +1998,19 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="17" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="16" t="n">
         <f aca="false">IF($A8="","",COUNTIF('Órdenes de Ingreso'!$K:$K,$A8))</f>
         <v>2</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="17" t="n">
         <f aca="false">IF($A8="","",SUMIF('Órdenes de Ingreso'!$K:$K,$A8,'Órdenes de Ingreso'!$M:$M))</f>
         <v>162.1</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="17" t="n">
         <f aca="false">IF($A8="","",SUMIF(Cortes!$B:$B,$A8,Cortes!$D:$D))</f>
         <v>0</v>
       </c>
@@ -1960,19 +2019,19 @@
         <v>162.1</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="17" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="16" t="n">
         <f aca="false">IF($A9="","",COUNTIF('Órdenes de Ingreso'!$K:$K,$A9))</f>
         <v>1</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="17" t="n">
         <f aca="false">IF($A9="","",SUMIF('Órdenes de Ingreso'!$K:$K,$A9,'Órdenes de Ingreso'!$M:$M))</f>
         <v>307.7</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="17" t="n">
         <f aca="false">IF($A9="","",SUMIF(Cortes!$B:$B,$A9,Cortes!$D:$D))</f>
         <v>0</v>
       </c>
@@ -1981,17 +2040,17 @@
         <v>307.7</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8"/>
-      <c r="B10" s="17" t="str">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7"/>
+      <c r="B10" s="16" t="str">
         <f aca="false">IF($A10="","",COUNTIF('Órdenes de Ingreso'!$K:$K,$A10))</f>
         <v/>
       </c>
-      <c r="C10" s="18" t="str">
+      <c r="C10" s="17" t="str">
         <f aca="false">IF($A10="","",SUMIF('Órdenes de Ingreso'!$K:$K,$A10,'Órdenes de Ingreso'!$M:$M))</f>
         <v/>
       </c>
-      <c r="D10" s="18" t="str">
+      <c r="D10" s="17" t="str">
         <f aca="false">IF($A10="","",SUMIF(Cortes!$B:$B,$A10,Cortes!$D:$D))</f>
         <v/>
       </c>
@@ -2000,17 +2059,17 @@
         <v/>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8"/>
-      <c r="B11" s="17" t="str">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7"/>
+      <c r="B11" s="16" t="str">
         <f aca="false">IF($A11="","",COUNTIF('Órdenes de Ingreso'!$K:$K,$A11))</f>
         <v/>
       </c>
-      <c r="C11" s="18" t="str">
+      <c r="C11" s="17" t="str">
         <f aca="false">IF($A11="","",SUMIF('Órdenes de Ingreso'!$K:$K,$A11,'Órdenes de Ingreso'!$M:$M))</f>
         <v/>
       </c>
-      <c r="D11" s="18" t="str">
+      <c r="D11" s="17" t="str">
         <f aca="false">IF($A11="","",SUMIF(Cortes!$B:$B,$A11,Cortes!$D:$D))</f>
         <v/>
       </c>
@@ -2047,123 +2106,123 @@
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="B2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>84</v>
       </c>
       <c r="D2" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
       <c r="D3" s="19"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="19"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
       <c r="D5" s="19"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
       <c r="D6" s="19"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
       <c r="D7" s="19"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
       <c r="D8" s="19"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
       <c r="D9" s="19"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
       <c r="D10" s="19"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
       <c r="D11" s="19"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2191,821 +2250,793 @@
   <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+    <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="E2" s="21"/>
+      <c r="F2" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="G2" s="7"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="B3" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="C3" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="E2" s="22"/>
-      <c r="F2" s="21" t="s">
+      <c r="D3" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G2" s="8"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="F3" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="G3" s="22" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="B5" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="C5" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="D5" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="23" t="n">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
+      <c r="E5" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="F5" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="G5" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="D5" s="24" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="B6" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="G5" s="24" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="8" t="n">
         <v>15900</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="26" t="n">
         <f aca="false">ROUND(F6*$G$3,0)</f>
         <v>3021</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="26" t="n">
         <f aca="false">C6*D6</f>
         <v>15900</v>
       </c>
-      <c r="G6" s="27" t="n">
+      <c r="G6" s="26" t="n">
         <f aca="false">F6+E6</f>
         <v>18921</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" s="9" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="24"/>
+      <c r="B7" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="26" t="n">
         <f aca="false">ROUND(F7*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="26" t="n">
         <f aca="false">C7*D7</f>
         <v>0</v>
       </c>
-      <c r="G7" s="27" t="n">
+      <c r="G7" s="26" t="n">
         <f aca="false">F7+E7</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" s="9" t="n">
+      <c r="A8" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="8" t="n">
         <v>15900</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>1.07</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="26" t="n">
         <f aca="false">ROUND(F8*$G$3,0)</f>
         <v>3232</v>
       </c>
-      <c r="F8" s="27" t="n">
+      <c r="F8" s="26" t="n">
         <f aca="false">C8*D8</f>
         <v>17013</v>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="G8" s="26" t="n">
         <f aca="false">F8+E8</f>
         <v>20245</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25"/>
-      <c r="B9" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="9" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="24"/>
+      <c r="B9" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="8" t="n">
         <v>4400</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>0.15</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="26" t="n">
         <f aca="false">ROUND(F9*$G$3,0)</f>
         <v>125</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="26" t="n">
         <f aca="false">C9*D9</f>
         <v>660</v>
       </c>
-      <c r="G9" s="27" t="n">
+      <c r="G9" s="26" t="n">
         <f aca="false">F9+E9</f>
         <v>785</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25"/>
-      <c r="B10" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" s="9" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="24"/>
+      <c r="B10" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="26" t="n">
         <f aca="false">ROUND(F10*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="26" t="n">
         <f aca="false">C10*D10</f>
         <v>0</v>
       </c>
-      <c r="G10" s="27" t="n">
+      <c r="G10" s="26" t="n">
         <f aca="false">F10+E10</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" s="9" t="n">
+      <c r="A11" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="26" t="n">
         <f aca="false">ROUND(F11*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="F11" s="26" t="n">
         <f aca="false">C11*D11</f>
         <v>0</v>
       </c>
-      <c r="G11" s="27" t="n">
+      <c r="G11" s="26" t="n">
         <f aca="false">F11+E11</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="C12" s="9" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="8" t="n">
         <v>1200</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="26" t="n">
         <f aca="false">ROUND(F12*$G$3,0)</f>
         <v>228</v>
       </c>
-      <c r="F12" s="27" t="n">
+      <c r="F12" s="26" t="n">
         <f aca="false">C12*D12</f>
         <v>1200</v>
       </c>
-      <c r="G12" s="27" t="n">
+      <c r="G12" s="26" t="n">
         <f aca="false">F12+E12</f>
         <v>1428</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="C13" s="9" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="8" t="n">
         <v>10700</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="26" t="n">
         <f aca="false">ROUND(F13*$G$3,0)</f>
         <v>2033</v>
       </c>
-      <c r="F13" s="27" t="n">
+      <c r="F13" s="26" t="n">
         <f aca="false">C13*D13</f>
         <v>10700</v>
       </c>
-      <c r="G13" s="27" t="n">
+      <c r="G13" s="26" t="n">
         <f aca="false">F13+E13</f>
         <v>12733</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" s="9" t="n">
+      <c r="A14" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="8" t="n">
         <v>700</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="26" t="n">
         <f aca="false">ROUND(F14*$G$3,0)</f>
         <v>133</v>
       </c>
-      <c r="F14" s="27" t="n">
+      <c r="F14" s="26" t="n">
         <f aca="false">C14*D14</f>
         <v>700</v>
       </c>
-      <c r="G14" s="27" t="n">
+      <c r="G14" s="26" t="n">
         <f aca="false">F14+E14</f>
         <v>833</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="25"/>
-      <c r="B15" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="C15" s="9" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="24"/>
+      <c r="B15" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="8" t="n">
         <v>87</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="26" t="n">
         <f aca="false">ROUND(F15*$G$3,0)</f>
         <v>17</v>
       </c>
-      <c r="F15" s="27" t="n">
+      <c r="F15" s="26" t="n">
         <f aca="false">C15*D15</f>
         <v>87</v>
       </c>
-      <c r="G15" s="27" t="n">
+      <c r="G15" s="26" t="n">
         <f aca="false">F15+E15</f>
         <v>104</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" s="9" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="9" t="n">
         <v>0.07</v>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="26" t="n">
         <f aca="false">ROUND(F16*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="27" t="n">
+      <c r="F16" s="26" t="n">
         <f aca="false">C16*D16</f>
         <v>0</v>
       </c>
-      <c r="G16" s="27" t="n">
+      <c r="G16" s="26" t="n">
         <f aca="false">F16+E16</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="9" t="n">
+      <c r="A17" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="8" t="n">
         <v>7000</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="27" t="n">
+      <c r="E17" s="26" t="n">
         <f aca="false">ROUND(F17*$G$3,0)</f>
         <v>1330</v>
       </c>
-      <c r="F17" s="27" t="n">
+      <c r="F17" s="26" t="n">
         <f aca="false">C17*D17</f>
         <v>7000</v>
       </c>
-      <c r="G17" s="27" t="n">
+      <c r="G17" s="26" t="n">
         <f aca="false">F17+E17</f>
         <v>8330</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="C18" s="9" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="8" t="n">
         <v>2100</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="27" t="n">
+      <c r="E18" s="26" t="n">
         <f aca="false">ROUND(F18*$G$3,0)</f>
         <v>399</v>
       </c>
-      <c r="F18" s="27" t="n">
+      <c r="F18" s="26" t="n">
         <f aca="false">C18*D18</f>
         <v>2100</v>
       </c>
-      <c r="G18" s="27" t="n">
+      <c r="G18" s="26" t="n">
         <f aca="false">F18+E18</f>
         <v>2499</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="C19" s="9" t="n">
+      <c r="A19" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E19" s="26" t="n">
         <f aca="false">ROUND(F19*$G$3,0)</f>
         <v>4</v>
       </c>
-      <c r="F19" s="27" t="n">
+      <c r="F19" s="26" t="n">
         <f aca="false">C19*D19</f>
         <v>20</v>
       </c>
-      <c r="G19" s="27" t="n">
+      <c r="G19" s="26" t="n">
         <f aca="false">F19+E19</f>
         <v>24</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="24"/>
+      <c r="B20" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="8" t="n">
         <v>123</v>
       </c>
-      <c r="C20" s="9" t="n">
-        <v>123</v>
-      </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="26" t="n">
         <f aca="false">ROUND(F20*$G$3,0)</f>
         <v>23</v>
       </c>
-      <c r="F20" s="27" t="n">
+      <c r="F20" s="26" t="n">
         <f aca="false">C20*D20</f>
         <v>123</v>
       </c>
-      <c r="G20" s="27" t="n">
+      <c r="G20" s="26" t="n">
         <f aca="false">F20+E20</f>
         <v>146</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="C21" s="9" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="27" t="n">
+      <c r="E21" s="26" t="n">
         <f aca="false">ROUND(F21*$G$3,0)</f>
         <v>2</v>
       </c>
-      <c r="F21" s="27" t="n">
+      <c r="F21" s="26" t="n">
         <f aca="false">C21*D21</f>
         <v>10</v>
       </c>
-      <c r="G21" s="27" t="n">
+      <c r="G21" s="26" t="n">
         <f aca="false">F21+E21</f>
         <v>12</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="C22" s="9" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="24"/>
+      <c r="B22" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" s="8" t="n">
         <v>180</v>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="27" t="n">
+      <c r="E22" s="26" t="n">
         <f aca="false">ROUND(F22*$G$3,0)</f>
         <v>34</v>
       </c>
-      <c r="F22" s="27" t="n">
+      <c r="F22" s="26" t="n">
         <f aca="false">C22*D22</f>
         <v>180</v>
       </c>
-      <c r="G22" s="27" t="n">
+      <c r="G22" s="26" t="n">
         <f aca="false">F22+E22</f>
         <v>214</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="C23" s="9" t="n">
+      <c r="A23" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="8" t="n">
         <v>278</v>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="27" t="n">
+      <c r="E23" s="26" t="n">
         <f aca="false">ROUND(F23*$G$3,0)</f>
         <v>53</v>
       </c>
-      <c r="F23" s="27" t="n">
+      <c r="F23" s="26" t="n">
         <f aca="false">C23*D23</f>
         <v>278</v>
       </c>
-      <c r="G23" s="27" t="n">
+      <c r="G23" s="26" t="n">
         <f aca="false">F23+E23</f>
         <v>331</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" s="9" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="24"/>
+      <c r="B24" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" s="8" t="n">
         <v>111</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="27" t="n">
+      <c r="E24" s="26" t="n">
         <f aca="false">ROUND(F24*$G$3,0)</f>
         <v>42</v>
       </c>
-      <c r="F24" s="27" t="n">
+      <c r="F24" s="26" t="n">
         <f aca="false">C24*D24</f>
         <v>222</v>
       </c>
-      <c r="G24" s="27" t="n">
+      <c r="G24" s="26" t="n">
         <f aca="false">F24+E24</f>
         <v>264</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="C25" s="9" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="24"/>
+      <c r="B25" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" s="8" t="n">
         <v>700</v>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="27" t="n">
+      <c r="E25" s="26" t="n">
         <f aca="false">ROUND(F25*$G$3,0)</f>
         <v>133</v>
       </c>
-      <c r="F25" s="27" t="n">
+      <c r="F25" s="26" t="n">
         <f aca="false">C25*D25</f>
         <v>700</v>
       </c>
-      <c r="G25" s="27" t="n">
+      <c r="G25" s="26" t="n">
         <f aca="false">F25+E25</f>
         <v>833</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="C26" s="9" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="24"/>
+      <c r="B26" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="27" t="n">
+      <c r="E26" s="26" t="n">
         <f aca="false">ROUND(F26*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F26" s="27" t="n">
+      <c r="F26" s="26" t="n">
         <f aca="false">C26*D26</f>
         <v>0</v>
       </c>
-      <c r="G26" s="27" t="n">
+      <c r="G26" s="26" t="n">
         <f aca="false">F26+E26</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="25"/>
-      <c r="B27" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="C27" s="9" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="24"/>
+      <c r="B27" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="27" t="n">
+      <c r="E27" s="26" t="n">
         <f aca="false">ROUND(F27*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="27" t="n">
+      <c r="F27" s="26" t="n">
         <f aca="false">C27*D27</f>
         <v>0</v>
       </c>
-      <c r="G27" s="27" t="n">
+      <c r="G27" s="26" t="n">
         <f aca="false">F27+E27</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="B28" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="C28" s="9" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="C28" s="8" t="n">
         <v>11000</v>
       </c>
-      <c r="D28" s="10" t="n">
+      <c r="D28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="27" t="n">
+      <c r="E28" s="26" t="n">
         <f aca="false">ROUND(F28*$G$3,0)</f>
         <v>2090</v>
       </c>
-      <c r="F28" s="27" t="n">
+      <c r="F28" s="26" t="n">
         <f aca="false">C28*D28</f>
         <v>11000</v>
       </c>
-      <c r="G28" s="27" t="n">
+      <c r="G28" s="26" t="n">
         <f aca="false">F28+E28</f>
         <v>13090</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="28"/>
-      <c r="B29" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="30" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="27"/>
+      <c r="B29" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="29" t="n">
         <f aca="false">SUM(F6:F28)</f>
         <v>67893</v>
       </c>
-      <c r="G29" s="30" t="n">
+      <c r="G29" s="29" t="n">
         <f aca="false">SUM(G6:G28)</f>
         <v>80792</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="B31" s="32"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="B32" s="33" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B32" s="30" t="n">
         <f aca="false">F29</f>
         <v>67893</v>
       </c>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-    </row>
-    <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="24" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="B33" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="C33" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="D33" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="E33" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="23" t="n">
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="B34" s="34" t="n">
+      <c r="B34" s="31" t="n">
         <f aca="false">ROUND($B$32*(1+A34)*(1+$G$3),0)</f>
         <v>121189</v>
       </c>
-      <c r="C34" s="35" t="n">
+      <c r="C34" s="32" t="n">
         <f aca="false">ROUND(B34/(1+$G$3),0)</f>
         <v>101839</v>
       </c>
-      <c r="D34" s="34" t="n">
+      <c r="D34" s="33" t="n">
         <f aca="false">B34-C34</f>
         <v>19350</v>
       </c>
-      <c r="E34" s="36" t="n">
+      <c r="E34" s="34" t="n">
         <f aca="false">IF(C34=0,0,(C34-$B$32)/C34)</f>
         <v>0.33333006019305</v>
       </c>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="23" t="n">
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="22" t="n">
         <v>0.65</v>
       </c>
-      <c r="B35" s="34" t="n">
+      <c r="B35" s="31" t="n">
         <f aca="false">ROUND($B$32*(1+A35)*(1+$G$3),0)</f>
         <v>133308</v>
       </c>
-      <c r="C35" s="35" t="n">
+      <c r="C35" s="32" t="n">
         <f aca="false">ROUND(B35/(1+$G$3),0)</f>
         <v>112024</v>
       </c>
-      <c r="D35" s="34" t="n">
+      <c r="D35" s="33" t="n">
         <f aca="false">B35-C35</f>
         <v>21284</v>
       </c>
-      <c r="E35" s="36" t="n">
+      <c r="E35" s="34" t="n">
         <f aca="false">IF(C35=0,0,(C35-$B$32)/C35)</f>
         <v>0.393942369492252</v>
       </c>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="23" t="n">
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="n">
         <v>0.8</v>
       </c>
-      <c r="B36" s="34" t="n">
+      <c r="B36" s="31" t="n">
         <f aca="false">ROUND($B$32*(1+A36)*(1+$G$3),0)</f>
         <v>145427</v>
       </c>
-      <c r="C36" s="35" t="n">
+      <c r="C36" s="32" t="n">
         <f aca="false">ROUND(B36/(1+$G$3),0)</f>
         <v>122208</v>
       </c>
-      <c r="D36" s="34" t="n">
+      <c r="D36" s="33" t="n">
         <f aca="false">B36-C36</f>
         <v>23219</v>
       </c>
-      <c r="E36" s="36" t="n">
+      <c r="E36" s="34" t="n">
         <f aca="false">IF(C36=0,0,(C36-$B$32)/C36)</f>
         <v>0.444447172034564</v>
       </c>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="32"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-    </row>
-    <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="B38" s="8"/>
-      <c r="C38" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="D38" s="8"/>
-      <c r="F38" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="G38" s="8"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="37"/>
+    </row>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="D38" s="7"/>
+      <c r="F38" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="G38" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="B40" s="35"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3033,6 +3064,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3044,48 +3076,47 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="6" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="36" t="s">
         <v>150</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="38" t="s">
-        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -3107,253 +3138,253 @@
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+    <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+    </row>
+    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="7"/>
+    </row>
+    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="39" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-    </row>
-    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="21" t="s">
+      <c r="B6" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="D4" s="8"/>
-    </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="D5" s="8"/>
-    </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="B6" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="D6" s="41" t="n">
+      <c r="D6" s="39" t="n">
         <f aca="false">IFERROR(VLOOKUP(B6,Inventario!$A$7:$E$20,5,0),0)</f>
         <v>69</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="D7" s="8"/>
+      <c r="A7" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="42" t="s">
-        <v>165</v>
+      <c r="A9" s="4" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="43" t="s">
-        <v>81</v>
+      <c r="A10" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="44"/>
-      <c r="B11" s="44"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
+      <c r="A11" s="41"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="44"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
+      <c r="A12" s="41"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="44"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
+      <c r="A13" s="41"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="44"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
+      <c r="A14" s="41"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="20" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
+      <c r="D18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="21" t="s">
+      <c r="B19" s="7"/>
+      <c r="C19" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="D17" s="8"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="s">
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="21" t="s">
+      <c r="B20" s="7"/>
+      <c r="C20" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="D18" s="8"/>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="D19" s="8"/>
-    </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="D20" s="8"/>
+      <c r="D20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="42" t="s">
+      <c r="A22" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="B23" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="D23" s="40" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="43" t="s">
+      <c r="E23" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="B23" s="43" t="s">
+      <c r="F23" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="G23" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="D23" s="43" t="s">
-        <v>179</v>
-      </c>
-      <c r="E23" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="F23" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="G23" s="43" t="s">
-        <v>182</v>
-      </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="45"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="45"/>
+      <c r="A24" s="42"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="42" t="s">
-        <v>183</v>
+      <c r="A26" s="4" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="46" t="s">
-        <v>184</v>
-      </c>
-      <c r="B27" s="46"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
+      <c r="A27" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="46"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
+      <c r="A28" s="43"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="43"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="46"/>
-      <c r="B29" s="46"/>
-      <c r="C29" s="46"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
+      <c r="A29" s="43"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="E31" s="8"/>
+      <c r="A31" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="E31" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3379,5 +3410,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/sheets/Produccion_Sheet_Plantilla.xlsx
+++ b/sheets/Produccion_Sheet_Plantilla.xlsx
@@ -14,7 +14,8 @@
     <sheet name="Cortes" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Precosteo (formato)" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Histórico Precosteo" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Orden de Corte (formato)" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Histórico Cortes" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Orden de Corte (formato)" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -82,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="182">
   <si>
     <t xml:space="preserve">Plantilla de Producción — Fase 1</t>
   </si>
@@ -141,52 +142,52 @@
     <t xml:space="preserve">Montserrat (equivalente de Gotham). Texto editable en azul #0C457A.</t>
   </si>
   <si>
-    <t xml:space="preserve">textilera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">numero_documento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tipo_documento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fecha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orden_compra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">numero_rollo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">serial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lote_fabrica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">referencia_tela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">descripcion_tela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ancho_cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">costo_metro_cop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codigo_interno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">barcode</t>
+    <t xml:space="preserve">Textilera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N° documento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo documento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orden de compra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N° rollo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lote fábrica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencia tela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descripción tela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancho (cm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo metro (COP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código interno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código de barras</t>
   </si>
   <si>
     <t xml:space="preserve">Primatela</t>
@@ -195,7 +196,7 @@
     <t xml:space="preserve">7572901088</t>
   </si>
   <si>
-    <t xml:space="preserve">remision</t>
+    <t xml:space="preserve">Remisión</t>
   </si>
   <si>
     <t xml:space="preserve">2025-10-29</t>
@@ -228,7 +229,7 @@
     <t xml:space="preserve">30-10002</t>
   </si>
   <si>
-    <t xml:space="preserve">lista_empaque</t>
+    <t xml:space="preserve">Lista de empaque</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-19</t>
@@ -267,7 +268,7 @@
     <t xml:space="preserve">FEMT16043</t>
   </si>
   <si>
-    <t xml:space="preserve">factura</t>
+    <t xml:space="preserve">Factura</t>
   </si>
   <si>
     <t xml:space="preserve">2026-02-12</t>
@@ -294,31 +295,31 @@
     <t xml:space="preserve">Rollos:</t>
   </si>
   <si>
-    <t xml:space="preserve">nombre_tela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nro_rollos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metros_recibidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metros_cortados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metros_disponibles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tela_nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">referencia_prenda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metros_usados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">responsable</t>
+    <t xml:space="preserve">Nombre tela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N° rollos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metros recibidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metros cortados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metros disponibles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tela (nombre)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencia prenda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metros usados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsable</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-26</t>
@@ -507,61 +508,58 @@
     <t xml:space="preserve">▶ Botón 'Guardar y firmar' (Apps Script): archiva en 'Histórico Precosteo' y limpia el formato a 0.</t>
   </si>
   <si>
-    <t xml:space="preserve">fecha_firma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ref</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">costo_total_sin_iva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">costo_total_con_iva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">precio_venta_con_iva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">autorizado_por</t>
+    <t xml:space="preserve">Fecha firma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo total sin IVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo total con IVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio venta con IVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autorizado por</t>
   </si>
   <si>
     <t xml:space="preserve">(las filas firmadas se agregan aquí automáticamente)</t>
   </si>
   <si>
+    <t xml:space="preserve">Consecutivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(las órdenes de corte firmadas se agregan aquí)</t>
+  </si>
+  <si>
     <t xml:space="preserve">          ORDEN DE CORTE</t>
   </si>
   <si>
     <t xml:space="preserve">Documento que autoriza al cortador a iniciar (luz verde)</t>
   </si>
   <si>
-    <t xml:space="preserve">Consecutivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha</t>
-  </si>
-  <si>
     <t xml:space="preserve">Referencia (prenda)</t>
   </si>
   <si>
-    <t xml:space="preserve">Tono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tela (nombre)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Disponible (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responsable</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha límite</t>
@@ -646,7 +644,7 @@
     <numFmt numFmtId="169" formatCode="0%"/>
     <numFmt numFmtId="170" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -708,9 +706,16 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
+      <color rgb="FF606060"/>
+      <name val="Montserrat"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <color rgb="FF213033"/>
-      <name val="Montserrat"/>
+      <name val="Libre Barcode 39"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -746,6 +751,13 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FF036A73"/>
+      <name val="Montserrat"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF213033"/>
       <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
@@ -938,7 +950,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -979,19 +991,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -999,19 +1015,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1019,7 +1039,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1031,19 +1051,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1055,7 +1075,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1063,7 +1083,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1079,15 +1099,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1095,15 +1115,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1613,24 +1633,25 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P201"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="26.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="9.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1683,7 +1704,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
@@ -1722,10 +1743,16 @@
       <c r="N2" s="8" t="n">
         <v>9800</v>
       </c>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O2" s="10" t="str">
+        <f aca="false">IF($A2="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v>ROLLO-2026-000001</v>
+      </c>
+      <c r="P2" s="11" t="str">
+        <f aca="false">IF(O2="","","*"&amp;O2&amp;"*")</f>
+        <v>*ROLLO-2026-000001*</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
         <v>35</v>
       </c>
@@ -1764,10 +1791,16 @@
       <c r="N3" s="8" t="n">
         <v>9800</v>
       </c>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O3" s="10" t="str">
+        <f aca="false">IF($A3="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v>ROLLO-2026-000002</v>
+      </c>
+      <c r="P3" s="11" t="str">
+        <f aca="false">IF(O3="","","*"&amp;O3&amp;"*")</f>
+        <v>*ROLLO-2026-000002*</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
         <v>46</v>
       </c>
@@ -1810,10 +1843,16 @@
       <c r="N4" s="8" t="n">
         <v>12500</v>
       </c>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O4" s="10" t="str">
+        <f aca="false">IF($A4="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v>ROLLO-2026-000003</v>
+      </c>
+      <c r="P4" s="11" t="str">
+        <f aca="false">IF(O4="","","*"&amp;O4&amp;"*")</f>
+        <v>*ROLLO-2026-000003*</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>46</v>
       </c>
@@ -1856,10 +1895,16 @@
       <c r="N5" s="8" t="n">
         <v>12500</v>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O5" s="10" t="str">
+        <f aca="false">IF($A5="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v>ROLLO-2026-000004</v>
+      </c>
+      <c r="P5" s="11" t="str">
+        <f aca="false">IF(O5="","","*"&amp;O5&amp;"*")</f>
+        <v>*ROLLO-2026-000004*</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
         <v>59</v>
       </c>
@@ -1896,13 +1941,1969 @@
       <c r="N6" s="8" t="n">
         <v>16000</v>
       </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
+      <c r="O6" s="10" t="str">
+        <f aca="false">IF($A6="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v>ROLLO-2026-000005</v>
+      </c>
+      <c r="P6" s="11" t="str">
+        <f aca="false">IF(O6="","","*"&amp;O6&amp;"*")</f>
+        <v>*ROLLO-2026-000005*</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O7" s="10" t="str">
+        <f aca="false">IF($A7="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P7" s="12" t="str">
+        <f aca="false">IF(O7="","","*"&amp;O7&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O8" s="10" t="str">
+        <f aca="false">IF($A8="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P8" s="12" t="str">
+        <f aca="false">IF(O8="","","*"&amp;O8&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O9" s="10" t="str">
+        <f aca="false">IF($A9="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P9" s="12" t="str">
+        <f aca="false">IF(O9="","","*"&amp;O9&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O10" s="10" t="str">
+        <f aca="false">IF($A10="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P10" s="12" t="str">
+        <f aca="false">IF(O10="","","*"&amp;O10&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O11" s="10" t="str">
+        <f aca="false">IF($A11="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P11" s="12" t="str">
+        <f aca="false">IF(O11="","","*"&amp;O11&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O12" s="10" t="str">
+        <f aca="false">IF($A12="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P12" s="12" t="str">
+        <f aca="false">IF(O12="","","*"&amp;O12&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O13" s="10" t="str">
+        <f aca="false">IF($A13="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P13" s="12" t="str">
+        <f aca="false">IF(O13="","","*"&amp;O13&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O14" s="10" t="str">
+        <f aca="false">IF($A14="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P14" s="12" t="str">
+        <f aca="false">IF(O14="","","*"&amp;O14&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O15" s="10" t="str">
+        <f aca="false">IF($A15="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P15" s="12" t="str">
+        <f aca="false">IF(O15="","","*"&amp;O15&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O16" s="10" t="str">
+        <f aca="false">IF($A16="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P16" s="12" t="str">
+        <f aca="false">IF(O16="","","*"&amp;O16&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O17" s="10" t="str">
+        <f aca="false">IF($A17="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P17" s="12" t="str">
+        <f aca="false">IF(O17="","","*"&amp;O17&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O18" s="10" t="str">
+        <f aca="false">IF($A18="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P18" s="12" t="str">
+        <f aca="false">IF(O18="","","*"&amp;O18&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O19" s="10" t="str">
+        <f aca="false">IF($A19="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P19" s="12" t="str">
+        <f aca="false">IF(O19="","","*"&amp;O19&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O20" s="10" t="str">
+        <f aca="false">IF($A20="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P20" s="12" t="str">
+        <f aca="false">IF(O20="","","*"&amp;O20&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O21" s="10" t="str">
+        <f aca="false">IF($A21="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P21" s="12" t="str">
+        <f aca="false">IF(O21="","","*"&amp;O21&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O22" s="10" t="str">
+        <f aca="false">IF($A22="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P22" s="12" t="str">
+        <f aca="false">IF(O22="","","*"&amp;O22&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O23" s="10" t="str">
+        <f aca="false">IF($A23="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P23" s="12" t="str">
+        <f aca="false">IF(O23="","","*"&amp;O23&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O24" s="10" t="str">
+        <f aca="false">IF($A24="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P24" s="12" t="str">
+        <f aca="false">IF(O24="","","*"&amp;O24&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O25" s="10" t="str">
+        <f aca="false">IF($A25="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P25" s="12" t="str">
+        <f aca="false">IF(O25="","","*"&amp;O25&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O26" s="10" t="str">
+        <f aca="false">IF($A26="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P26" s="12" t="str">
+        <f aca="false">IF(O26="","","*"&amp;O26&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O27" s="10" t="str">
+        <f aca="false">IF($A27="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P27" s="12" t="str">
+        <f aca="false">IF(O27="","","*"&amp;O27&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O28" s="10" t="str">
+        <f aca="false">IF($A28="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P28" s="12" t="str">
+        <f aca="false">IF(O28="","","*"&amp;O28&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O29" s="10" t="str">
+        <f aca="false">IF($A29="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P29" s="12" t="str">
+        <f aca="false">IF(O29="","","*"&amp;O29&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O30" s="10" t="str">
+        <f aca="false">IF($A30="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P30" s="12" t="str">
+        <f aca="false">IF(O30="","","*"&amp;O30&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O31" s="10" t="str">
+        <f aca="false">IF($A31="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P31" s="12" t="str">
+        <f aca="false">IF(O31="","","*"&amp;O31&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O32" s="10" t="str">
+        <f aca="false">IF($A32="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P32" s="12" t="str">
+        <f aca="false">IF(O32="","","*"&amp;O32&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O33" s="10" t="str">
+        <f aca="false">IF($A33="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P33" s="12" t="str">
+        <f aca="false">IF(O33="","","*"&amp;O33&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O34" s="10" t="str">
+        <f aca="false">IF($A34="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P34" s="12" t="str">
+        <f aca="false">IF(O34="","","*"&amp;O34&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O35" s="10" t="str">
+        <f aca="false">IF($A35="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P35" s="12" t="str">
+        <f aca="false">IF(O35="","","*"&amp;O35&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O36" s="10" t="str">
+        <f aca="false">IF($A36="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P36" s="12" t="str">
+        <f aca="false">IF(O36="","","*"&amp;O36&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O37" s="10" t="str">
+        <f aca="false">IF($A37="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P37" s="12" t="str">
+        <f aca="false">IF(O37="","","*"&amp;O37&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O38" s="10" t="str">
+        <f aca="false">IF($A38="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P38" s="12" t="str">
+        <f aca="false">IF(O38="","","*"&amp;O38&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O39" s="10" t="str">
+        <f aca="false">IF($A39="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P39" s="12" t="str">
+        <f aca="false">IF(O39="","","*"&amp;O39&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O40" s="10" t="str">
+        <f aca="false">IF($A40="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P40" s="12" t="str">
+        <f aca="false">IF(O40="","","*"&amp;O40&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O41" s="10" t="str">
+        <f aca="false">IF($A41="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P41" s="12" t="str">
+        <f aca="false">IF(O41="","","*"&amp;O41&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O42" s="10" t="str">
+        <f aca="false">IF($A42="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P42" s="12" t="str">
+        <f aca="false">IF(O42="","","*"&amp;O42&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O43" s="10" t="str">
+        <f aca="false">IF($A43="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P43" s="12" t="str">
+        <f aca="false">IF(O43="","","*"&amp;O43&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O44" s="10" t="str">
+        <f aca="false">IF($A44="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P44" s="12" t="str">
+        <f aca="false">IF(O44="","","*"&amp;O44&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O45" s="10" t="str">
+        <f aca="false">IF($A45="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P45" s="12" t="str">
+        <f aca="false">IF(O45="","","*"&amp;O45&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O46" s="10" t="str">
+        <f aca="false">IF($A46="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P46" s="12" t="str">
+        <f aca="false">IF(O46="","","*"&amp;O46&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O47" s="10" t="str">
+        <f aca="false">IF($A47="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P47" s="12" t="str">
+        <f aca="false">IF(O47="","","*"&amp;O47&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O48" s="10" t="str">
+        <f aca="false">IF($A48="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P48" s="12" t="str">
+        <f aca="false">IF(O48="","","*"&amp;O48&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O49" s="10" t="str">
+        <f aca="false">IF($A49="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P49" s="12" t="str">
+        <f aca="false">IF(O49="","","*"&amp;O49&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O50" s="10" t="str">
+        <f aca="false">IF($A50="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P50" s="12" t="str">
+        <f aca="false">IF(O50="","","*"&amp;O50&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O51" s="10" t="str">
+        <f aca="false">IF($A51="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P51" s="12" t="str">
+        <f aca="false">IF(O51="","","*"&amp;O51&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O52" s="10" t="str">
+        <f aca="false">IF($A52="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P52" s="12" t="str">
+        <f aca="false">IF(O52="","","*"&amp;O52&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O53" s="10" t="str">
+        <f aca="false">IF($A53="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P53" s="12" t="str">
+        <f aca="false">IF(O53="","","*"&amp;O53&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O54" s="10" t="str">
+        <f aca="false">IF($A54="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P54" s="12" t="str">
+        <f aca="false">IF(O54="","","*"&amp;O54&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O55" s="10" t="str">
+        <f aca="false">IF($A55="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P55" s="12" t="str">
+        <f aca="false">IF(O55="","","*"&amp;O55&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O56" s="10" t="str">
+        <f aca="false">IF($A56="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P56" s="12" t="str">
+        <f aca="false">IF(O56="","","*"&amp;O56&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O57" s="10" t="str">
+        <f aca="false">IF($A57="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P57" s="12" t="str">
+        <f aca="false">IF(O57="","","*"&amp;O57&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O58" s="10" t="str">
+        <f aca="false">IF($A58="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P58" s="12" t="str">
+        <f aca="false">IF(O58="","","*"&amp;O58&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O59" s="10" t="str">
+        <f aca="false">IF($A59="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P59" s="12" t="str">
+        <f aca="false">IF(O59="","","*"&amp;O59&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O60" s="10" t="str">
+        <f aca="false">IF($A60="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P60" s="12" t="str">
+        <f aca="false">IF(O60="","","*"&amp;O60&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O61" s="10" t="str">
+        <f aca="false">IF($A61="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P61" s="12" t="str">
+        <f aca="false">IF(O61="","","*"&amp;O61&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O62" s="10" t="str">
+        <f aca="false">IF($A62="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P62" s="12" t="str">
+        <f aca="false">IF(O62="","","*"&amp;O62&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O63" s="10" t="str">
+        <f aca="false">IF($A63="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P63" s="12" t="str">
+        <f aca="false">IF(O63="","","*"&amp;O63&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O64" s="10" t="str">
+        <f aca="false">IF($A64="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P64" s="12" t="str">
+        <f aca="false">IF(O64="","","*"&amp;O64&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O65" s="10" t="str">
+        <f aca="false">IF($A65="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P65" s="12" t="str">
+        <f aca="false">IF(O65="","","*"&amp;O65&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O66" s="10" t="str">
+        <f aca="false">IF($A66="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P66" s="12" t="str">
+        <f aca="false">IF(O66="","","*"&amp;O66&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O67" s="10" t="str">
+        <f aca="false">IF($A67="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P67" s="12" t="str">
+        <f aca="false">IF(O67="","","*"&amp;O67&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O68" s="10" t="str">
+        <f aca="false">IF($A68="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P68" s="12" t="str">
+        <f aca="false">IF(O68="","","*"&amp;O68&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O69" s="10" t="str">
+        <f aca="false">IF($A69="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P69" s="12" t="str">
+        <f aca="false">IF(O69="","","*"&amp;O69&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O70" s="10" t="str">
+        <f aca="false">IF($A70="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P70" s="12" t="str">
+        <f aca="false">IF(O70="","","*"&amp;O70&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O71" s="10" t="str">
+        <f aca="false">IF($A71="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P71" s="12" t="str">
+        <f aca="false">IF(O71="","","*"&amp;O71&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O72" s="10" t="str">
+        <f aca="false">IF($A72="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P72" s="12" t="str">
+        <f aca="false">IF(O72="","","*"&amp;O72&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O73" s="10" t="str">
+        <f aca="false">IF($A73="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P73" s="12" t="str">
+        <f aca="false">IF(O73="","","*"&amp;O73&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O74" s="10" t="str">
+        <f aca="false">IF($A74="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P74" s="12" t="str">
+        <f aca="false">IF(O74="","","*"&amp;O74&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O75" s="10" t="str">
+        <f aca="false">IF($A75="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P75" s="12" t="str">
+        <f aca="false">IF(O75="","","*"&amp;O75&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O76" s="10" t="str">
+        <f aca="false">IF($A76="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P76" s="12" t="str">
+        <f aca="false">IF(O76="","","*"&amp;O76&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O77" s="10" t="str">
+        <f aca="false">IF($A77="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P77" s="12" t="str">
+        <f aca="false">IF(O77="","","*"&amp;O77&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O78" s="10" t="str">
+        <f aca="false">IF($A78="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P78" s="12" t="str">
+        <f aca="false">IF(O78="","","*"&amp;O78&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O79" s="10" t="str">
+        <f aca="false">IF($A79="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P79" s="12" t="str">
+        <f aca="false">IF(O79="","","*"&amp;O79&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O80" s="10" t="str">
+        <f aca="false">IF($A80="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P80" s="12" t="str">
+        <f aca="false">IF(O80="","","*"&amp;O80&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O81" s="10" t="str">
+        <f aca="false">IF($A81="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P81" s="12" t="str">
+        <f aca="false">IF(O81="","","*"&amp;O81&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O82" s="10" t="str">
+        <f aca="false">IF($A82="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P82" s="12" t="str">
+        <f aca="false">IF(O82="","","*"&amp;O82&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O83" s="10" t="str">
+        <f aca="false">IF($A83="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P83" s="12" t="str">
+        <f aca="false">IF(O83="","","*"&amp;O83&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O84" s="10" t="str">
+        <f aca="false">IF($A84="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P84" s="12" t="str">
+        <f aca="false">IF(O84="","","*"&amp;O84&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O85" s="10" t="str">
+        <f aca="false">IF($A85="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P85" s="12" t="str">
+        <f aca="false">IF(O85="","","*"&amp;O85&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O86" s="10" t="str">
+        <f aca="false">IF($A86="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P86" s="12" t="str">
+        <f aca="false">IF(O86="","","*"&amp;O86&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O87" s="10" t="str">
+        <f aca="false">IF($A87="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P87" s="12" t="str">
+        <f aca="false">IF(O87="","","*"&amp;O87&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O88" s="10" t="str">
+        <f aca="false">IF($A88="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P88" s="12" t="str">
+        <f aca="false">IF(O88="","","*"&amp;O88&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O89" s="10" t="str">
+        <f aca="false">IF($A89="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P89" s="12" t="str">
+        <f aca="false">IF(O89="","","*"&amp;O89&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O90" s="10" t="str">
+        <f aca="false">IF($A90="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P90" s="12" t="str">
+        <f aca="false">IF(O90="","","*"&amp;O90&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O91" s="10" t="str">
+        <f aca="false">IF($A91="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P91" s="12" t="str">
+        <f aca="false">IF(O91="","","*"&amp;O91&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O92" s="10" t="str">
+        <f aca="false">IF($A92="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P92" s="12" t="str">
+        <f aca="false">IF(O92="","","*"&amp;O92&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O93" s="10" t="str">
+        <f aca="false">IF($A93="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P93" s="12" t="str">
+        <f aca="false">IF(O93="","","*"&amp;O93&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O94" s="10" t="str">
+        <f aca="false">IF($A94="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P94" s="12" t="str">
+        <f aca="false">IF(O94="","","*"&amp;O94&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O95" s="10" t="str">
+        <f aca="false">IF($A95="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P95" s="12" t="str">
+        <f aca="false">IF(O95="","","*"&amp;O95&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O96" s="10" t="str">
+        <f aca="false">IF($A96="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P96" s="12" t="str">
+        <f aca="false">IF(O96="","","*"&amp;O96&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O97" s="10" t="str">
+        <f aca="false">IF($A97="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P97" s="12" t="str">
+        <f aca="false">IF(O97="","","*"&amp;O97&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O98" s="10" t="str">
+        <f aca="false">IF($A98="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P98" s="12" t="str">
+        <f aca="false">IF(O98="","","*"&amp;O98&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O99" s="10" t="str">
+        <f aca="false">IF($A99="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P99" s="12" t="str">
+        <f aca="false">IF(O99="","","*"&amp;O99&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O100" s="10" t="str">
+        <f aca="false">IF($A100="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P100" s="12" t="str">
+        <f aca="false">IF(O100="","","*"&amp;O100&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O101" s="10" t="str">
+        <f aca="false">IF($A101="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P101" s="12" t="str">
+        <f aca="false">IF(O101="","","*"&amp;O101&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O102" s="10" t="str">
+        <f aca="false">IF($A102="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P102" s="12" t="str">
+        <f aca="false">IF(O102="","","*"&amp;O102&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O103" s="10" t="str">
+        <f aca="false">IF($A103="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P103" s="12" t="str">
+        <f aca="false">IF(O103="","","*"&amp;O103&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O104" s="10" t="str">
+        <f aca="false">IF($A104="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P104" s="12" t="str">
+        <f aca="false">IF(O104="","","*"&amp;O104&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O105" s="10" t="str">
+        <f aca="false">IF($A105="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P105" s="12" t="str">
+        <f aca="false">IF(O105="","","*"&amp;O105&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O106" s="10" t="str">
+        <f aca="false">IF($A106="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P106" s="12" t="str">
+        <f aca="false">IF(O106="","","*"&amp;O106&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O107" s="10" t="str">
+        <f aca="false">IF($A107="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P107" s="12" t="str">
+        <f aca="false">IF(O107="","","*"&amp;O107&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O108" s="10" t="str">
+        <f aca="false">IF($A108="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P108" s="12" t="str">
+        <f aca="false">IF(O108="","","*"&amp;O108&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O109" s="10" t="str">
+        <f aca="false">IF($A109="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P109" s="12" t="str">
+        <f aca="false">IF(O109="","","*"&amp;O109&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O110" s="10" t="str">
+        <f aca="false">IF($A110="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P110" s="12" t="str">
+        <f aca="false">IF(O110="","","*"&amp;O110&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O111" s="10" t="str">
+        <f aca="false">IF($A111="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P111" s="12" t="str">
+        <f aca="false">IF(O111="","","*"&amp;O111&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O112" s="10" t="str">
+        <f aca="false">IF($A112="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P112" s="12" t="str">
+        <f aca="false">IF(O112="","","*"&amp;O112&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O113" s="10" t="str">
+        <f aca="false">IF($A113="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P113" s="12" t="str">
+        <f aca="false">IF(O113="","","*"&amp;O113&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O114" s="10" t="str">
+        <f aca="false">IF($A114="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P114" s="12" t="str">
+        <f aca="false">IF(O114="","","*"&amp;O114&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O115" s="10" t="str">
+        <f aca="false">IF($A115="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P115" s="12" t="str">
+        <f aca="false">IF(O115="","","*"&amp;O115&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O116" s="10" t="str">
+        <f aca="false">IF($A116="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P116" s="12" t="str">
+        <f aca="false">IF(O116="","","*"&amp;O116&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O117" s="10" t="str">
+        <f aca="false">IF($A117="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P117" s="12" t="str">
+        <f aca="false">IF(O117="","","*"&amp;O117&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O118" s="10" t="str">
+        <f aca="false">IF($A118="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P118" s="12" t="str">
+        <f aca="false">IF(O118="","","*"&amp;O118&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O119" s="10" t="str">
+        <f aca="false">IF($A119="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P119" s="12" t="str">
+        <f aca="false">IF(O119="","","*"&amp;O119&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O120" s="10" t="str">
+        <f aca="false">IF($A120="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P120" s="12" t="str">
+        <f aca="false">IF(O120="","","*"&amp;O120&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O121" s="10" t="str">
+        <f aca="false">IF($A121="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P121" s="12" t="str">
+        <f aca="false">IF(O121="","","*"&amp;O121&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O122" s="10" t="str">
+        <f aca="false">IF($A122="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P122" s="12" t="str">
+        <f aca="false">IF(O122="","","*"&amp;O122&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O123" s="10" t="str">
+        <f aca="false">IF($A123="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P123" s="12" t="str">
+        <f aca="false">IF(O123="","","*"&amp;O123&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O124" s="10" t="str">
+        <f aca="false">IF($A124="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P124" s="12" t="str">
+        <f aca="false">IF(O124="","","*"&amp;O124&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O125" s="10" t="str">
+        <f aca="false">IF($A125="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P125" s="12" t="str">
+        <f aca="false">IF(O125="","","*"&amp;O125&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O126" s="10" t="str">
+        <f aca="false">IF($A126="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P126" s="12" t="str">
+        <f aca="false">IF(O126="","","*"&amp;O126&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O127" s="10" t="str">
+        <f aca="false">IF($A127="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P127" s="12" t="str">
+        <f aca="false">IF(O127="","","*"&amp;O127&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O128" s="10" t="str">
+        <f aca="false">IF($A128="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P128" s="12" t="str">
+        <f aca="false">IF(O128="","","*"&amp;O128&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O129" s="10" t="str">
+        <f aca="false">IF($A129="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P129" s="12" t="str">
+        <f aca="false">IF(O129="","","*"&amp;O129&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O130" s="10" t="str">
+        <f aca="false">IF($A130="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P130" s="12" t="str">
+        <f aca="false">IF(O130="","","*"&amp;O130&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O131" s="10" t="str">
+        <f aca="false">IF($A131="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P131" s="12" t="str">
+        <f aca="false">IF(O131="","","*"&amp;O131&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O132" s="10" t="str">
+        <f aca="false">IF($A132="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P132" s="12" t="str">
+        <f aca="false">IF(O132="","","*"&amp;O132&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O133" s="10" t="str">
+        <f aca="false">IF($A133="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P133" s="12" t="str">
+        <f aca="false">IF(O133="","","*"&amp;O133&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O134" s="10" t="str">
+        <f aca="false">IF($A134="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P134" s="12" t="str">
+        <f aca="false">IF(O134="","","*"&amp;O134&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O135" s="10" t="str">
+        <f aca="false">IF($A135="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P135" s="12" t="str">
+        <f aca="false">IF(O135="","","*"&amp;O135&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O136" s="10" t="str">
+        <f aca="false">IF($A136="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P136" s="12" t="str">
+        <f aca="false">IF(O136="","","*"&amp;O136&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O137" s="10" t="str">
+        <f aca="false">IF($A137="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P137" s="12" t="str">
+        <f aca="false">IF(O137="","","*"&amp;O137&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O138" s="10" t="str">
+        <f aca="false">IF($A138="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P138" s="12" t="str">
+        <f aca="false">IF(O138="","","*"&amp;O138&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O139" s="10" t="str">
+        <f aca="false">IF($A139="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P139" s="12" t="str">
+        <f aca="false">IF(O139="","","*"&amp;O139&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O140" s="10" t="str">
+        <f aca="false">IF($A140="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P140" s="12" t="str">
+        <f aca="false">IF(O140="","","*"&amp;O140&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O141" s="10" t="str">
+        <f aca="false">IF($A141="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P141" s="12" t="str">
+        <f aca="false">IF(O141="","","*"&amp;O141&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O142" s="10" t="str">
+        <f aca="false">IF($A142="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P142" s="12" t="str">
+        <f aca="false">IF(O142="","","*"&amp;O142&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O143" s="10" t="str">
+        <f aca="false">IF($A143="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P143" s="12" t="str">
+        <f aca="false">IF(O143="","","*"&amp;O143&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O144" s="10" t="str">
+        <f aca="false">IF($A144="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P144" s="12" t="str">
+        <f aca="false">IF(O144="","","*"&amp;O144&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O145" s="10" t="str">
+        <f aca="false">IF($A145="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P145" s="12" t="str">
+        <f aca="false">IF(O145="","","*"&amp;O145&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O146" s="10" t="str">
+        <f aca="false">IF($A146="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P146" s="12" t="str">
+        <f aca="false">IF(O146="","","*"&amp;O146&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O147" s="10" t="str">
+        <f aca="false">IF($A147="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P147" s="12" t="str">
+        <f aca="false">IF(O147="","","*"&amp;O147&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O148" s="10" t="str">
+        <f aca="false">IF($A148="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P148" s="12" t="str">
+        <f aca="false">IF(O148="","","*"&amp;O148&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O149" s="10" t="str">
+        <f aca="false">IF($A149="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P149" s="12" t="str">
+        <f aca="false">IF(O149="","","*"&amp;O149&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O150" s="10" t="str">
+        <f aca="false">IF($A150="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P150" s="12" t="str">
+        <f aca="false">IF(O150="","","*"&amp;O150&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O151" s="10" t="str">
+        <f aca="false">IF($A151="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P151" s="12" t="str">
+        <f aca="false">IF(O151="","","*"&amp;O151&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O152" s="10" t="str">
+        <f aca="false">IF($A152="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P152" s="12" t="str">
+        <f aca="false">IF(O152="","","*"&amp;O152&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O153" s="10" t="str">
+        <f aca="false">IF($A153="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P153" s="12" t="str">
+        <f aca="false">IF(O153="","","*"&amp;O153&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O154" s="10" t="str">
+        <f aca="false">IF($A154="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P154" s="12" t="str">
+        <f aca="false">IF(O154="","","*"&amp;O154&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O155" s="10" t="str">
+        <f aca="false">IF($A155="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P155" s="12" t="str">
+        <f aca="false">IF(O155="","","*"&amp;O155&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O156" s="10" t="str">
+        <f aca="false">IF($A156="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P156" s="12" t="str">
+        <f aca="false">IF(O156="","","*"&amp;O156&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O157" s="10" t="str">
+        <f aca="false">IF($A157="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P157" s="12" t="str">
+        <f aca="false">IF(O157="","","*"&amp;O157&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O158" s="10" t="str">
+        <f aca="false">IF($A158="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P158" s="12" t="str">
+        <f aca="false">IF(O158="","","*"&amp;O158&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O159" s="10" t="str">
+        <f aca="false">IF($A159="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P159" s="12" t="str">
+        <f aca="false">IF(O159="","","*"&amp;O159&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O160" s="10" t="str">
+        <f aca="false">IF($A160="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P160" s="12" t="str">
+        <f aca="false">IF(O160="","","*"&amp;O160&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O161" s="10" t="str">
+        <f aca="false">IF($A161="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P161" s="12" t="str">
+        <f aca="false">IF(O161="","","*"&amp;O161&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O162" s="10" t="str">
+        <f aca="false">IF($A162="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P162" s="12" t="str">
+        <f aca="false">IF(O162="","","*"&amp;O162&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O163" s="10" t="str">
+        <f aca="false">IF($A163="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P163" s="12" t="str">
+        <f aca="false">IF(O163="","","*"&amp;O163&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O164" s="10" t="str">
+        <f aca="false">IF($A164="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P164" s="12" t="str">
+        <f aca="false">IF(O164="","","*"&amp;O164&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O165" s="10" t="str">
+        <f aca="false">IF($A165="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P165" s="12" t="str">
+        <f aca="false">IF(O165="","","*"&amp;O165&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O166" s="10" t="str">
+        <f aca="false">IF($A166="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P166" s="12" t="str">
+        <f aca="false">IF(O166="","","*"&amp;O166&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O167" s="10" t="str">
+        <f aca="false">IF($A167="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P167" s="12" t="str">
+        <f aca="false">IF(O167="","","*"&amp;O167&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O168" s="10" t="str">
+        <f aca="false">IF($A168="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P168" s="12" t="str">
+        <f aca="false">IF(O168="","","*"&amp;O168&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O169" s="10" t="str">
+        <f aca="false">IF($A169="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P169" s="12" t="str">
+        <f aca="false">IF(O169="","","*"&amp;O169&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O170" s="10" t="str">
+        <f aca="false">IF($A170="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P170" s="12" t="str">
+        <f aca="false">IF(O170="","","*"&amp;O170&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O171" s="10" t="str">
+        <f aca="false">IF($A171="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P171" s="12" t="str">
+        <f aca="false">IF(O171="","","*"&amp;O171&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O172" s="10" t="str">
+        <f aca="false">IF($A172="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P172" s="12" t="str">
+        <f aca="false">IF(O172="","","*"&amp;O172&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O173" s="10" t="str">
+        <f aca="false">IF($A173="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P173" s="12" t="str">
+        <f aca="false">IF(O173="","","*"&amp;O173&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O174" s="10" t="str">
+        <f aca="false">IF($A174="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P174" s="12" t="str">
+        <f aca="false">IF(O174="","","*"&amp;O174&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O175" s="10" t="str">
+        <f aca="false">IF($A175="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P175" s="12" t="str">
+        <f aca="false">IF(O175="","","*"&amp;O175&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O176" s="10" t="str">
+        <f aca="false">IF($A176="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P176" s="12" t="str">
+        <f aca="false">IF(O176="","","*"&amp;O176&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O177" s="10" t="str">
+        <f aca="false">IF($A177="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P177" s="12" t="str">
+        <f aca="false">IF(O177="","","*"&amp;O177&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O178" s="10" t="str">
+        <f aca="false">IF($A178="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P178" s="12" t="str">
+        <f aca="false">IF(O178="","","*"&amp;O178&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O179" s="10" t="str">
+        <f aca="false">IF($A179="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P179" s="12" t="str">
+        <f aca="false">IF(O179="","","*"&amp;O179&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O180" s="10" t="str">
+        <f aca="false">IF($A180="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P180" s="12" t="str">
+        <f aca="false">IF(O180="","","*"&amp;O180&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O181" s="10" t="str">
+        <f aca="false">IF($A181="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P181" s="12" t="str">
+        <f aca="false">IF(O181="","","*"&amp;O181&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O182" s="10" t="str">
+        <f aca="false">IF($A182="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P182" s="12" t="str">
+        <f aca="false">IF(O182="","","*"&amp;O182&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O183" s="10" t="str">
+        <f aca="false">IF($A183="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P183" s="12" t="str">
+        <f aca="false">IF(O183="","","*"&amp;O183&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O184" s="10" t="str">
+        <f aca="false">IF($A184="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P184" s="12" t="str">
+        <f aca="false">IF(O184="","","*"&amp;O184&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O185" s="10" t="str">
+        <f aca="false">IF($A185="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P185" s="12" t="str">
+        <f aca="false">IF(O185="","","*"&amp;O185&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O186" s="10" t="str">
+        <f aca="false">IF($A186="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P186" s="12" t="str">
+        <f aca="false">IF(O186="","","*"&amp;O186&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O187" s="10" t="str">
+        <f aca="false">IF($A187="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P187" s="12" t="str">
+        <f aca="false">IF(O187="","","*"&amp;O187&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O188" s="10" t="str">
+        <f aca="false">IF($A188="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P188" s="12" t="str">
+        <f aca="false">IF(O188="","","*"&amp;O188&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O189" s="10" t="str">
+        <f aca="false">IF($A189="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P189" s="12" t="str">
+        <f aca="false">IF(O189="","","*"&amp;O189&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O190" s="10" t="str">
+        <f aca="false">IF($A190="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P190" s="12" t="str">
+        <f aca="false">IF(O190="","","*"&amp;O190&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O191" s="10" t="str">
+        <f aca="false">IF($A191="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P191" s="12" t="str">
+        <f aca="false">IF(O191="","","*"&amp;O191&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O192" s="10" t="str">
+        <f aca="false">IF($A192="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P192" s="12" t="str">
+        <f aca="false">IF(O192="","","*"&amp;O192&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O193" s="10" t="str">
+        <f aca="false">IF($A193="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P193" s="12" t="str">
+        <f aca="false">IF(O193="","","*"&amp;O193&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O194" s="10" t="str">
+        <f aca="false">IF($A194="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P194" s="12" t="str">
+        <f aca="false">IF(O194="","","*"&amp;O194&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O195" s="10" t="str">
+        <f aca="false">IF($A195="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P195" s="12" t="str">
+        <f aca="false">IF(O195="","","*"&amp;O195&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O196" s="10" t="str">
+        <f aca="false">IF($A196="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P196" s="12" t="str">
+        <f aca="false">IF(O196="","","*"&amp;O196&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O197" s="10" t="str">
+        <f aca="false">IF($A197="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P197" s="12" t="str">
+        <f aca="false">IF(O197="","","*"&amp;O197&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O198" s="10" t="str">
+        <f aca="false">IF($A198="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P198" s="12" t="str">
+        <f aca="false">IF(O198="","","*"&amp;O198&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O199" s="10" t="str">
+        <f aca="false">IF($A199="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P199" s="12" t="str">
+        <f aca="false">IF(O199="","","*"&amp;O199&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O200" s="10" t="str">
+        <f aca="false">IF($A200="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P200" s="12" t="str">
+        <f aca="false">IF(O200="","","*"&amp;O200&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O201" s="10" t="str">
+        <f aca="false">IF($A201="","","ROLLO-2026-"&amp;TEXT(ROW()-1,"000000"))</f>
+        <v/>
+      </c>
+      <c r="P201" s="12" t="str">
+        <f aca="false">IF(O201="","","*"&amp;O201&amp;"*")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C1000" type="list">
-      <formula1>"remision,factura,lista_empaque,consulta"</formula1>
+      <formula1>"Remisión,Factura,Lista de empaque,Consulta"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -1926,54 +3927,53 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="15" t="n">
         <f aca="false">IFERROR(VLOOKUP(B3,$A$7:$E$20,2,0),0)</f>
         <v>2</v>
       </c>
-      <c r="E3" s="14" t="str">
+      <c r="E3" s="16" t="str">
         <f aca="false">IFERROR("Disponible: "&amp;TEXT(VLOOKUP(B3,$A$7:$E$20,5,0),"#,##0.0")&amp;" m","")</f>
         <v>Disponible: 69.0 m</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="17" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1981,19 +3981,19 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="18" t="n">
         <f aca="false">IF($A7="","",COUNTIF('Órdenes de Ingreso'!$K:$K,$A7))</f>
         <v>2</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="19" t="n">
         <f aca="false">IF($A7="","",SUMIF('Órdenes de Ingreso'!$K:$K,$A7,'Órdenes de Ingreso'!$M:$M))</f>
         <v>99</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="19" t="n">
         <f aca="false">IF($A7="","",SUMIF(Cortes!$B:$B,$A7,Cortes!$D:$D))</f>
         <v>30</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">IF($A7="","",$C7-$D7)</f>
         <v>69</v>
       </c>
@@ -2002,19 +4002,19 @@
       <c r="A8" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="18" t="n">
         <f aca="false">IF($A8="","",COUNTIF('Órdenes de Ingreso'!$K:$K,$A8))</f>
         <v>2</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="19" t="n">
         <f aca="false">IF($A8="","",SUMIF('Órdenes de Ingreso'!$K:$K,$A8,'Órdenes de Ingreso'!$M:$M))</f>
         <v>162.1</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="19" t="n">
         <f aca="false">IF($A8="","",SUMIF(Cortes!$B:$B,$A8,Cortes!$D:$D))</f>
         <v>0</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">IF($A8="","",$C8-$D8)</f>
         <v>162.1</v>
       </c>
@@ -2023,57 +4023,57 @@
       <c r="A9" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="18" t="n">
         <f aca="false">IF($A9="","",COUNTIF('Órdenes de Ingreso'!$K:$K,$A9))</f>
         <v>1</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="19" t="n">
         <f aca="false">IF($A9="","",SUMIF('Órdenes de Ingreso'!$K:$K,$A9,'Órdenes de Ingreso'!$M:$M))</f>
         <v>307.7</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="19" t="n">
         <f aca="false">IF($A9="","",SUMIF(Cortes!$B:$B,$A9,Cortes!$D:$D))</f>
         <v>0</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="20" t="n">
         <f aca="false">IF($A9="","",$C9-$D9)</f>
         <v>307.7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7"/>
-      <c r="B10" s="16" t="str">
+      <c r="B10" s="18" t="str">
         <f aca="false">IF($A10="","",COUNTIF('Órdenes de Ingreso'!$K:$K,$A10))</f>
         <v/>
       </c>
-      <c r="C10" s="17" t="str">
+      <c r="C10" s="19" t="str">
         <f aca="false">IF($A10="","",SUMIF('Órdenes de Ingreso'!$K:$K,$A10,'Órdenes de Ingreso'!$M:$M))</f>
         <v/>
       </c>
-      <c r="D10" s="17" t="str">
+      <c r="D10" s="19" t="str">
         <f aca="false">IF($A10="","",SUMIF(Cortes!$B:$B,$A10,Cortes!$D:$D))</f>
         <v/>
       </c>
-      <c r="E10" s="18" t="str">
+      <c r="E10" s="20" t="str">
         <f aca="false">IF($A10="","",$C10-$D10)</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7"/>
-      <c r="B11" s="16" t="str">
+      <c r="B11" s="18" t="str">
         <f aca="false">IF($A11="","",COUNTIF('Órdenes de Ingreso'!$K:$K,$A11))</f>
         <v/>
       </c>
-      <c r="C11" s="17" t="str">
+      <c r="C11" s="19" t="str">
         <f aca="false">IF($A11="","",SUMIF('Órdenes de Ingreso'!$K:$K,$A11,'Órdenes de Ingreso'!$M:$M))</f>
         <v/>
       </c>
-      <c r="D11" s="17" t="str">
+      <c r="D11" s="19" t="str">
         <f aca="false">IF($A11="","",SUMIF(Cortes!$B:$B,$A11,Cortes!$D:$D))</f>
         <v/>
       </c>
-      <c r="E11" s="18" t="str">
+      <c r="E11" s="20" t="str">
         <f aca="false">IF($A11="","",$C11-$D11)</f>
         <v/>
       </c>
@@ -2106,7 +4106,7 @@
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
@@ -2144,7 +4144,7 @@
       <c r="C2" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="19" t="n">
+      <c r="D2" s="21" t="n">
         <v>30</v>
       </c>
       <c r="E2" s="7"/>
@@ -2156,7 +4156,7 @@
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
-      <c r="D3" s="19"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
     </row>
@@ -2164,7 +4164,7 @@
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
-      <c r="D4" s="19"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
     </row>
@@ -2172,7 +4172,7 @@
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="19"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
     </row>
@@ -2180,7 +4180,7 @@
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="19"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
     </row>
@@ -2188,7 +4188,7 @@
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="19"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
     </row>
@@ -2196,7 +4196,7 @@
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="19"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
     </row>
@@ -2204,7 +4204,7 @@
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="19"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
     </row>
@@ -2212,7 +4212,7 @@
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="19"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
     </row>
@@ -2220,7 +4220,7 @@
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="19"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
     </row>
@@ -2260,83 +4260,83 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>83</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="21"/>
-      <c r="F2" s="20" t="s">
+      <c r="E2" s="23"/>
+      <c r="F2" s="22" t="s">
         <v>87</v>
       </c>
       <c r="G2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="22" t="s">
         <v>88</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="22" t="s">
         <v>90</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="G3" s="22" t="n">
+      <c r="G3" s="24" t="n">
         <v>0.19</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23" t="s">
+    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" s="25" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="27" t="s">
         <v>101</v>
       </c>
       <c r="C6" s="8" t="n">
@@ -2345,22 +4345,22 @@
       <c r="D6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="28" t="n">
         <f aca="false">ROUND(F6*$G$3,0)</f>
         <v>3021</v>
       </c>
-      <c r="F6" s="26" t="n">
+      <c r="F6" s="28" t="n">
         <f aca="false">C6*D6</f>
         <v>15900</v>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="28" t="n">
         <f aca="false">F6+E6</f>
         <v>18921</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24"/>
-      <c r="B7" s="25" t="s">
+      <c r="A7" s="26"/>
+      <c r="B7" s="27" t="s">
         <v>102</v>
       </c>
       <c r="C7" s="8" t="n">
@@ -2369,24 +4369,24 @@
       <c r="D7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="26" t="n">
+      <c r="E7" s="28" t="n">
         <f aca="false">ROUND(F7*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="26" t="n">
+      <c r="F7" s="28" t="n">
         <f aca="false">C7*D7</f>
         <v>0</v>
       </c>
-      <c r="G7" s="26" t="n">
+      <c r="G7" s="28" t="n">
         <f aca="false">F7+E7</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="27" t="s">
         <v>88</v>
       </c>
       <c r="C8" s="8" t="n">
@@ -2395,22 +4395,22 @@
       <c r="D8" s="9" t="n">
         <v>1.07</v>
       </c>
-      <c r="E8" s="26" t="n">
+      <c r="E8" s="28" t="n">
         <f aca="false">ROUND(F8*$G$3,0)</f>
         <v>3232</v>
       </c>
-      <c r="F8" s="26" t="n">
+      <c r="F8" s="28" t="n">
         <f aca="false">C8*D8</f>
         <v>17013</v>
       </c>
-      <c r="G8" s="26" t="n">
+      <c r="G8" s="28" t="n">
         <f aca="false">F8+E8</f>
         <v>20245</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24"/>
-      <c r="B9" s="25" t="s">
+      <c r="A9" s="26"/>
+      <c r="B9" s="27" t="s">
         <v>104</v>
       </c>
       <c r="C9" s="8" t="n">
@@ -2419,22 +4419,22 @@
       <c r="D9" s="9" t="n">
         <v>0.15</v>
       </c>
-      <c r="E9" s="26" t="n">
+      <c r="E9" s="28" t="n">
         <f aca="false">ROUND(F9*$G$3,0)</f>
         <v>125</v>
       </c>
-      <c r="F9" s="26" t="n">
+      <c r="F9" s="28" t="n">
         <f aca="false">C9*D9</f>
         <v>660</v>
       </c>
-      <c r="G9" s="26" t="n">
+      <c r="G9" s="28" t="n">
         <f aca="false">F9+E9</f>
         <v>785</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24"/>
-      <c r="B10" s="25" t="s">
+      <c r="A10" s="26"/>
+      <c r="B10" s="27" t="s">
         <v>105</v>
       </c>
       <c r="C10" s="8" t="n">
@@ -2443,24 +4443,24 @@
       <c r="D10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="26" t="n">
+      <c r="E10" s="28" t="n">
         <f aca="false">ROUND(F10*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="26" t="n">
+      <c r="F10" s="28" t="n">
         <f aca="false">C10*D10</f>
         <v>0</v>
       </c>
-      <c r="G10" s="26" t="n">
+      <c r="G10" s="28" t="n">
         <f aca="false">F10+E10</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="27" t="s">
         <v>107</v>
       </c>
       <c r="C11" s="8" t="n">
@@ -2469,22 +4469,22 @@
       <c r="D11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="26" t="n">
+      <c r="E11" s="28" t="n">
         <f aca="false">ROUND(F11*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="26" t="n">
+      <c r="F11" s="28" t="n">
         <f aca="false">C11*D11</f>
         <v>0</v>
       </c>
-      <c r="G11" s="26" t="n">
+      <c r="G11" s="28" t="n">
         <f aca="false">F11+E11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25" t="s">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27" t="s">
         <v>108</v>
       </c>
       <c r="C12" s="8" t="n">
@@ -2493,24 +4493,24 @@
       <c r="D12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="26" t="n">
+      <c r="E12" s="28" t="n">
         <f aca="false">ROUND(F12*$G$3,0)</f>
         <v>228</v>
       </c>
-      <c r="F12" s="26" t="n">
+      <c r="F12" s="28" t="n">
         <f aca="false">C12*D12</f>
         <v>1200</v>
       </c>
-      <c r="G12" s="26" t="n">
+      <c r="G12" s="28" t="n">
         <f aca="false">F12+E12</f>
         <v>1428</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="27" t="s">
         <v>110</v>
       </c>
       <c r="C13" s="8" t="n">
@@ -2519,24 +4519,24 @@
       <c r="D13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="26" t="n">
+      <c r="E13" s="28" t="n">
         <f aca="false">ROUND(F13*$G$3,0)</f>
         <v>2033</v>
       </c>
-      <c r="F13" s="26" t="n">
+      <c r="F13" s="28" t="n">
         <f aca="false">C13*D13</f>
         <v>10700</v>
       </c>
-      <c r="G13" s="26" t="n">
+      <c r="G13" s="28" t="n">
         <f aca="false">F13+E13</f>
         <v>12733</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="27" t="s">
         <v>112</v>
       </c>
       <c r="C14" s="8" t="n">
@@ -2545,22 +4545,22 @@
       <c r="D14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="26" t="n">
+      <c r="E14" s="28" t="n">
         <f aca="false">ROUND(F14*$G$3,0)</f>
         <v>133</v>
       </c>
-      <c r="F14" s="26" t="n">
+      <c r="F14" s="28" t="n">
         <f aca="false">C14*D14</f>
         <v>700</v>
       </c>
-      <c r="G14" s="26" t="n">
+      <c r="G14" s="28" t="n">
         <f aca="false">F14+E14</f>
         <v>833</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25" t="s">
+      <c r="A15" s="26"/>
+      <c r="B15" s="27" t="s">
         <v>113</v>
       </c>
       <c r="C15" s="8" t="n">
@@ -2569,22 +4569,22 @@
       <c r="D15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="26" t="n">
+      <c r="E15" s="28" t="n">
         <f aca="false">ROUND(F15*$G$3,0)</f>
         <v>17</v>
       </c>
-      <c r="F15" s="26" t="n">
+      <c r="F15" s="28" t="n">
         <f aca="false">C15*D15</f>
         <v>87</v>
       </c>
-      <c r="G15" s="26" t="n">
+      <c r="G15" s="28" t="n">
         <f aca="false">F15+E15</f>
         <v>104</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25" t="s">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27" t="s">
         <v>114</v>
       </c>
       <c r="C16" s="8" t="n">
@@ -2593,24 +4593,24 @@
       <c r="D16" s="9" t="n">
         <v>0.07</v>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E16" s="28" t="n">
         <f aca="false">ROUND(F16*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="26" t="n">
+      <c r="F16" s="28" t="n">
         <f aca="false">C16*D16</f>
         <v>0</v>
       </c>
-      <c r="G16" s="26" t="n">
+      <c r="G16" s="28" t="n">
         <f aca="false">F16+E16</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="27" t="s">
         <v>115</v>
       </c>
       <c r="C17" s="8" t="n">
@@ -2619,22 +4619,22 @@
       <c r="D17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="28" t="n">
         <f aca="false">ROUND(F17*$G$3,0)</f>
         <v>1330</v>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="28" t="n">
         <f aca="false">C17*D17</f>
         <v>7000</v>
       </c>
-      <c r="G17" s="26" t="n">
+      <c r="G17" s="28" t="n">
         <f aca="false">F17+E17</f>
         <v>8330</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="24"/>
-      <c r="B18" s="25" t="s">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27" t="s">
         <v>116</v>
       </c>
       <c r="C18" s="8" t="n">
@@ -2643,24 +4643,24 @@
       <c r="D18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="28" t="n">
         <f aca="false">ROUND(F18*$G$3,0)</f>
         <v>399</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="28" t="n">
         <f aca="false">C18*D18</f>
         <v>2100</v>
       </c>
-      <c r="G18" s="26" t="n">
+      <c r="G18" s="28" t="n">
         <f aca="false">F18+E18</f>
         <v>2499</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="27" t="s">
         <v>118</v>
       </c>
       <c r="C19" s="8" t="n">
@@ -2669,22 +4669,22 @@
       <c r="D19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="28" t="n">
         <f aca="false">ROUND(F19*$G$3,0)</f>
         <v>4</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="28" t="n">
         <f aca="false">C19*D19</f>
         <v>20</v>
       </c>
-      <c r="G19" s="26" t="n">
+      <c r="G19" s="28" t="n">
         <f aca="false">F19+E19</f>
         <v>24</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25" t="s">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27" t="s">
         <v>119</v>
       </c>
       <c r="C20" s="8" t="n">
@@ -2693,22 +4693,22 @@
       <c r="D20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="26" t="n">
+      <c r="E20" s="28" t="n">
         <f aca="false">ROUND(F20*$G$3,0)</f>
         <v>23</v>
       </c>
-      <c r="F20" s="26" t="n">
+      <c r="F20" s="28" t="n">
         <f aca="false">C20*D20</f>
         <v>123</v>
       </c>
-      <c r="G20" s="26" t="n">
+      <c r="G20" s="28" t="n">
         <f aca="false">F20+E20</f>
         <v>146</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25" t="s">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27" t="s">
         <v>120</v>
       </c>
       <c r="C21" s="8" t="n">
@@ -2717,22 +4717,22 @@
       <c r="D21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="26" t="n">
+      <c r="E21" s="28" t="n">
         <f aca="false">ROUND(F21*$G$3,0)</f>
         <v>2</v>
       </c>
-      <c r="F21" s="26" t="n">
+      <c r="F21" s="28" t="n">
         <f aca="false">C21*D21</f>
         <v>10</v>
       </c>
-      <c r="G21" s="26" t="n">
+      <c r="G21" s="28" t="n">
         <f aca="false">F21+E21</f>
         <v>12</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24"/>
-      <c r="B22" s="25" t="s">
+      <c r="A22" s="26"/>
+      <c r="B22" s="27" t="s">
         <v>121</v>
       </c>
       <c r="C22" s="8" t="n">
@@ -2741,24 +4741,24 @@
       <c r="D22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="26" t="n">
+      <c r="E22" s="28" t="n">
         <f aca="false">ROUND(F22*$G$3,0)</f>
         <v>34</v>
       </c>
-      <c r="F22" s="26" t="n">
+      <c r="F22" s="28" t="n">
         <f aca="false">C22*D22</f>
         <v>180</v>
       </c>
-      <c r="G22" s="26" t="n">
+      <c r="G22" s="28" t="n">
         <f aca="false">F22+E22</f>
         <v>214</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="27" t="s">
         <v>123</v>
       </c>
       <c r="C23" s="8" t="n">
@@ -2767,22 +4767,22 @@
       <c r="D23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="26" t="n">
+      <c r="E23" s="28" t="n">
         <f aca="false">ROUND(F23*$G$3,0)</f>
         <v>53</v>
       </c>
-      <c r="F23" s="26" t="n">
+      <c r="F23" s="28" t="n">
         <f aca="false">C23*D23</f>
         <v>278</v>
       </c>
-      <c r="G23" s="26" t="n">
+      <c r="G23" s="28" t="n">
         <f aca="false">F23+E23</f>
         <v>331</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25" t="s">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27" t="s">
         <v>124</v>
       </c>
       <c r="C24" s="8" t="n">
@@ -2791,22 +4791,22 @@
       <c r="D24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="26" t="n">
+      <c r="E24" s="28" t="n">
         <f aca="false">ROUND(F24*$G$3,0)</f>
         <v>42</v>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="28" t="n">
         <f aca="false">C24*D24</f>
         <v>222</v>
       </c>
-      <c r="G24" s="26" t="n">
+      <c r="G24" s="28" t="n">
         <f aca="false">F24+E24</f>
         <v>264</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25" t="s">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27" t="s">
         <v>125</v>
       </c>
       <c r="C25" s="8" t="n">
@@ -2815,22 +4815,22 @@
       <c r="D25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="26" t="n">
+      <c r="E25" s="28" t="n">
         <f aca="false">ROUND(F25*$G$3,0)</f>
         <v>133</v>
       </c>
-      <c r="F25" s="26" t="n">
+      <c r="F25" s="28" t="n">
         <f aca="false">C25*D25</f>
         <v>700</v>
       </c>
-      <c r="G25" s="26" t="n">
+      <c r="G25" s="28" t="n">
         <f aca="false">F25+E25</f>
         <v>833</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24"/>
-      <c r="B26" s="25" t="s">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27" t="s">
         <v>126</v>
       </c>
       <c r="C26" s="8" t="n">
@@ -2839,22 +4839,22 @@
       <c r="D26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="26" t="n">
+      <c r="E26" s="28" t="n">
         <f aca="false">ROUND(F26*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F26" s="26" t="n">
+      <c r="F26" s="28" t="n">
         <f aca="false">C26*D26</f>
         <v>0</v>
       </c>
-      <c r="G26" s="26" t="n">
+      <c r="G26" s="28" t="n">
         <f aca="false">F26+E26</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="24"/>
-      <c r="B27" s="25" t="s">
+      <c r="A27" s="26"/>
+      <c r="B27" s="27" t="s">
         <v>127</v>
       </c>
       <c r="C27" s="8" t="n">
@@ -2863,24 +4863,24 @@
       <c r="D27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="26" t="n">
+      <c r="E27" s="28" t="n">
         <f aca="false">ROUND(F27*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="26" t="n">
+      <c r="F27" s="28" t="n">
         <f aca="false">C27*D27</f>
         <v>0</v>
       </c>
-      <c r="G27" s="26" t="n">
+      <c r="G27" s="28" t="n">
         <f aca="false">F27+E27</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24" t="s">
+      <c r="A28" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="B28" s="25" t="s">
+      <c r="B28" s="27" t="s">
         <v>128</v>
       </c>
       <c r="C28" s="8" t="n">
@@ -2889,32 +4889,32 @@
       <c r="D28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="26" t="n">
+      <c r="E28" s="28" t="n">
         <f aca="false">ROUND(F28*$G$3,0)</f>
         <v>2090</v>
       </c>
-      <c r="F28" s="26" t="n">
+      <c r="F28" s="28" t="n">
         <f aca="false">C28*D28</f>
         <v>11000</v>
       </c>
-      <c r="G28" s="26" t="n">
+      <c r="G28" s="28" t="n">
         <f aca="false">F28+E28</f>
         <v>13090</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="27"/>
-      <c r="B29" s="28" t="s">
+      <c r="A29" s="29"/>
+      <c r="B29" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="29" t="n">
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="31" t="n">
         <f aca="false">SUM(F6:F28)</f>
         <v>67893</v>
       </c>
-      <c r="G29" s="29" t="n">
+      <c r="G29" s="31" t="n">
         <f aca="false">SUM(G6:G28)</f>
         <v>80792</v>
       </c>
@@ -2925,118 +4925,118 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="B32" s="30" t="n">
+      <c r="B32" s="32" t="n">
         <f aca="false">F29</f>
         <v>67893</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="23" t="s">
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="B33" s="23" t="s">
+      <c r="B33" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C33" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="D33" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="E33" s="23" t="s">
+      <c r="E33" s="25" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="22" t="n">
+      <c r="A34" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="B34" s="31" t="n">
+      <c r="B34" s="33" t="n">
         <f aca="false">ROUND($B$32*(1+A34)*(1+$G$3),0)</f>
         <v>121189</v>
       </c>
-      <c r="C34" s="32" t="n">
+      <c r="C34" s="34" t="n">
         <f aca="false">ROUND(B34/(1+$G$3),0)</f>
         <v>101839</v>
       </c>
-      <c r="D34" s="33" t="n">
+      <c r="D34" s="35" t="n">
         <f aca="false">B34-C34</f>
         <v>19350</v>
       </c>
-      <c r="E34" s="34" t="n">
+      <c r="E34" s="36" t="n">
         <f aca="false">IF(C34=0,0,(C34-$B$32)/C34)</f>
         <v>0.33333006019305</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="22" t="n">
+      <c r="A35" s="24" t="n">
         <v>0.65</v>
       </c>
-      <c r="B35" s="31" t="n">
+      <c r="B35" s="33" t="n">
         <f aca="false">ROUND($B$32*(1+A35)*(1+$G$3),0)</f>
         <v>133308</v>
       </c>
-      <c r="C35" s="32" t="n">
+      <c r="C35" s="34" t="n">
         <f aca="false">ROUND(B35/(1+$G$3),0)</f>
         <v>112024</v>
       </c>
-      <c r="D35" s="33" t="n">
+      <c r="D35" s="35" t="n">
         <f aca="false">B35-C35</f>
         <v>21284</v>
       </c>
-      <c r="E35" s="34" t="n">
+      <c r="E35" s="36" t="n">
         <f aca="false">IF(C35=0,0,(C35-$B$32)/C35)</f>
         <v>0.393942369492252</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="22" t="n">
+      <c r="A36" s="24" t="n">
         <v>0.8</v>
       </c>
-      <c r="B36" s="31" t="n">
+      <c r="B36" s="33" t="n">
         <f aca="false">ROUND($B$32*(1+A36)*(1+$G$3),0)</f>
         <v>145427</v>
       </c>
-      <c r="C36" s="32" t="n">
+      <c r="C36" s="34" t="n">
         <f aca="false">ROUND(B36/(1+$G$3),0)</f>
         <v>122208</v>
       </c>
-      <c r="D36" s="33" t="n">
+      <c r="D36" s="35" t="n">
         <f aca="false">B36-C36</f>
         <v>23219</v>
       </c>
-      <c r="E36" s="34" t="n">
+      <c r="E36" s="36" t="n">
         <f aca="false">IF(C36=0,0,(C36-$B$32)/C36)</f>
         <v>0.444447172034564</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="22" t="s">
         <v>137</v>
       </c>
       <c r="B38" s="7"/>
-      <c r="C38" s="20" t="s">
+      <c r="C38" s="22" t="s">
         <v>138</v>
       </c>
       <c r="D38" s="7"/>
-      <c r="F38" s="20" t="s">
+      <c r="F38" s="22" t="s">
         <v>139</v>
       </c>
       <c r="G38" s="7"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="35" t="s">
+      <c r="A40" s="37" t="s">
         <v>140</v>
       </c>
-      <c r="B40" s="35"/>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="35"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3053,7 +5053,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B38" type="list">
-      <formula1>"borrador,autorizada"</formula1>
+      <formula1>"Borrador,Autorizada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -3077,12 +5077,13 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3115,7 +5116,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="38" t="s">
         <v>150</v>
       </c>
     </row>
@@ -3135,254 +5136,314 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="38" t="s">
+        <v>154</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+    </row>
+    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-    </row>
-    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
-        <v>153</v>
-      </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="20" t="s">
-        <v>154</v>
+      <c r="C4" s="22" t="s">
+        <v>22</v>
       </c>
       <c r="D4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>155</v>
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="22" t="s">
+        <v>157</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="20" t="s">
-        <v>156</v>
+      <c r="C5" s="22" t="s">
+        <v>27</v>
       </c>
       <c r="D5" s="7"/>
     </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="B6" s="38" t="s">
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="D6" s="39" t="n">
+      <c r="D6" s="41" t="n">
         <f aca="false">IFERROR(VLOOKUP(B6,Inventario!$A$7:$E$20,5,0),0)</f>
         <v>69</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="20" t="s">
+      <c r="D7" s="7"/>
+    </row>
+    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="D7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="43"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+    </row>
+    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+    </row>
+    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="43"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+    </row>
+    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="43"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+    </row>
+    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="40" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="41"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-    </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="41"/>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-    </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="41"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="41"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="22" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
+      <c r="B17" s="7"/>
+      <c r="C17" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="20" t="s">
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="D17" s="7"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
+      <c r="B18" s="7"/>
+      <c r="C18" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="20" t="s">
+      <c r="D18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="D18" s="7"/>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="20" t="s">
+      <c r="B19" s="7"/>
+      <c r="C19" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="20" t="s">
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="D19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20" t="s">
+      <c r="B20" s="7"/>
+      <c r="C20" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="20" t="s">
+      <c r="D20" s="7"/>
+    </row>
+    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="42" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="40" t="s">
+      <c r="B23" s="42" t="s">
         <v>172</v>
       </c>
-      <c r="B23" s="40" t="s">
+      <c r="C23" s="42" t="s">
         <v>173</v>
       </c>
-      <c r="C23" s="40" t="s">
+      <c r="D23" s="42" t="s">
         <v>174</v>
       </c>
-      <c r="D23" s="40" t="s">
+      <c r="E23" s="42" t="s">
         <v>175</v>
       </c>
-      <c r="E23" s="40" t="s">
+      <c r="F23" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="F23" s="40" t="s">
+      <c r="G23" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="G23" s="40" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="44"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+    </row>
+    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="42"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="42"/>
-    </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="45" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="43" t="s">
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+    </row>
+    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="45"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+    </row>
+    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="45"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+    </row>
+    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="B27" s="43"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-    </row>
-    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="43"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="43"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-    </row>
-    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="43"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-    </row>
-    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="s">
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="22" t="s">
         <v>181</v>
-      </c>
-      <c r="B31" s="21"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="20" t="s">
-        <v>182</v>
       </c>
       <c r="E31" s="7"/>
     </row>
@@ -3399,7 +5460,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E31" type="list">
-      <formula1>"borrador,autorizada,en_proceso,cortada"</formula1>
+      <formula1>"Borrador,Autorizada,En proceso,Cortada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/sheets/Produccion_Sheet_Plantilla.xlsx
+++ b/sheets/Produccion_Sheet_Plantilla.xlsx
@@ -11,11 +11,16 @@
     <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Órdenes de Ingreso" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Inventario" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Cortes" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Inventario de Insumos" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Precosteo (formato)" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Histórico Precosteo" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Histórico Cortes" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Orden de Corte (formato)" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Orden de Corte (formato)" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Remisión de Insumos" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Informe de Corte" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Cortes" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Histórico Precosteo" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Detalle Precosteo" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Histórico Cortes" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Remisiones Insumos" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -60,7 +65,7 @@
 </comments>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>conexión</author>
@@ -83,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="254">
   <si>
     <t xml:space="preserve">Plantilla de Producción — Fase 1</t>
   </si>
@@ -310,202 +315,457 @@
     <t xml:space="preserve">Metros disponibles</t>
   </si>
   <si>
+    <t xml:space="preserve">Código</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insumo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Categoría</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock inicial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entradas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salidas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock disponible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock mínimo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alerta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confección</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marquilla talla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bandera Colombia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Botón 27 L pasta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apliques Profintex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entretela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empaque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pretinera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrucción lavado impresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hilo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INS-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cremallera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          PRECOSTEO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14500-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOMBRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKINNY OSCURO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOTO (link)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERBENA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSCURO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVA %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CATEGORIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALOR UNITARIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANTIDAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL SIN IVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL CON IVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIRTY JEANS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRECIO TELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRECIO COMPLEMENTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FORRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPLEMENTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROCESO EN MP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BORDADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROCESO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONFECCION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSUMO CONFECCION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIERRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARQUILLA TALLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANDERA COLOMBIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAVANDERIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TERMINACION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSUMO EMPAQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CODIGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRETINERA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSTRUCCION LAVADO IMPRESA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMPAQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSUMO TERMINACION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTON 27 L PASTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REMACHE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APLIQUES PROFINTEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENTRETELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GASTOS FIJOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COSTO TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRECIO SUGERIDO DE VENTA (CON IVA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo base (sin IVA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margen %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRECIO VENTA (con IVA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio antes de IVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVA 19%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margen real %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTORIZADO POR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FECHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">▶ Botón 'Guardar y firmar' (Apps Script): archiva en 'Histórico Precosteo' y limpia el formato a 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          ORDEN DE CORTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planeación de corte — autoriza al cortador (luz verde). No descuenta inventario.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consecutivo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tela (nombre)</t>
   </si>
   <si>
+    <t xml:space="preserve">Disponible (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REFERENCIAS A CORTAR — curva por tallas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rend. teórico (m/prenda)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumo teórico (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROLLOS DE ESTA TELA (inventario — automático)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDICACIONES AL CORTADOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Sentido de la tela, defectos a evitar, notas de calidad, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTORIZADO POR (firma)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          REMISIÓN DE INSUMOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confeccionista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destinatario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencia / Orden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entregado por</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recibido por</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menú MALE'DENIM -&gt; Generar remisión de insumos: archiva en 'Remisiones Insumos' (descuenta stock) y limpia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          INFORME DE CORTE — teórico vs real</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POR REFERENCIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencia / Cortador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cortes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantidad prog.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumo teórico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumo real</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diferencia (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF 14500-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POR CORTADOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cortador 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cortador 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diferencia positiva = se gastó más tela que el teórico. Consumo real se cruza al cerrar el corte.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Referencia prenda</t>
   </si>
   <si>
     <t xml:space="preserve">Metros usados</t>
   </si>
   <si>
-    <t xml:space="preserve">Responsable</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-06-26</t>
   </si>
   <si>
-    <t xml:space="preserve">REF 14500-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cortador 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          PRECOSTEO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14500-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOMBRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SKINNY OSCURO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOTO (link)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERBENA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSCURO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVA %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATEGORIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALOR UNITARIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANTIDAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL SIN IVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL CON IVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIRTY JEANS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRECIO TELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRECIO COMPLEMENTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FORRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPLEMENTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROCESO EN MP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BORDADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROCESO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONFECCION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSUMO CONFECCION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIERRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARQUILLA TALLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANDERA COLOMBIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAVANDERIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TERMINACION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSUMO EMPAQUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CODIGO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRETINERA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSTRUCCION LAVADO IMPRESA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMPAQUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSUMO TERMINACION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOTON 27 L PASTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REMACHE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GARRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APLIQUES PROFINTEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENTRETELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GASTOS FIJOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COSTO TOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRECIO SUGERIDO DE VENTA (CON IVA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Costo base (sin IVA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margen %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRECIO VENTA (con IVA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Precio antes de IVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVA 19%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margen real %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTORIZADO POR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FECHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">▶ Botón 'Guardar y firmar' (Apps Script): archiva en 'Histórico Precosteo' y limpia el formato a 0.</t>
+    <t xml:space="preserve">ID</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha firma</t>
@@ -538,10 +798,49 @@
     <t xml:space="preserve">(las filas firmadas se agregan aquí automáticamente)</t>
   </si>
   <si>
-    <t xml:space="preserve">Consecutivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referencia</t>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor unitario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total sin IVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total con IVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(el detalle línea por línea de cada precosteo firmado se agrega aquí)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantidad programada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rend. teórico</t>
   </si>
   <si>
     <t xml:space="preserve">Firma</t>
@@ -550,92 +849,14 @@
     <t xml:space="preserve">(las órdenes de corte firmadas se agregan aquí)</t>
   </si>
   <si>
-    <t xml:space="preserve">          ORDEN DE CORTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Documento que autoriza al cortador a iniciar (luz verde)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referencia (prenda)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disponible (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha límite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROLLOS ASIGNADOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRAZO Y TENDIDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Largo trazo (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nº capas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prendas por trazo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prendas estimadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rend. teórico (m/prenda)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumo real</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diferencia %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merma (% o m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CURVA DE TALLAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INDICACIONES AL CORTADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Sentido de la tela, defectos a evitar, notas de calidad, etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTORIZADO POR (firma)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estado</t>
+    <t xml:space="preserve">(las remisiones generadas se agregan aquí)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
@@ -643,8 +864,10 @@
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
     <numFmt numFmtId="169" formatCode="0%"/>
     <numFmt numFmtId="170" formatCode="0.0%"/>
+    <numFmt numFmtId="171" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="172" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -772,6 +995,14 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF990012"/>
+      <name val="Montserrat"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF213033"/>
       <name val="Montserrat"/>
@@ -818,16 +1049,23 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF999999"/>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF213033"/>
       <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Montserrat"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
       <sz val="9"/>
-      <color rgb="FF0C457A"/>
+      <color rgb="FF999999"/>
       <name val="Montserrat"/>
       <family val="0"/>
       <charset val="1"/>
@@ -950,7 +1188,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="61">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1035,11 +1273,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1051,15 +1301,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1075,7 +1325,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1083,15 +1333,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1099,7 +1341,83 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1107,32 +1425,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1154,7 +1452,7 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF990012"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
@@ -1321,6 +1619,92 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="732960" cy="247320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>676080</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>228240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="676080" cy="228240"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>618840</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>209160</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="618840" cy="209160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1514,6 +1898,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFE1E1DF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A4:B18"/>
@@ -1628,9 +2013,296 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF606060"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="60" t="s">
+        <v>235</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF606060"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="60" t="s">
+        <v>240</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF606060"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:S2"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="6" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="60" t="s">
+        <v>252</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF606060"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="60" t="s">
+        <v>253</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF036A73"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P201"/>
@@ -3921,6 +4593,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF036A73"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E11"/>
@@ -4101,136 +4774,546 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF036A73"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="22" t="n">
+        <f aca="false">SUMIF('Remisiones Insumos'!$E:$E,$B2,'Remisiones Insumos'!$F:$F)</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="23" t="n">
+        <f aca="false">E2+F2-G2</f>
+        <v>500</v>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="J2" s="24" t="str">
+        <f aca="false">IF($H2&lt;=$I2,"REPONER","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="22" t="n">
+        <f aca="false">SUMIF('Remisiones Insumos'!$E:$E,$B3,'Remisiones Insumos'!$F:$F)</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="23" t="n">
+        <f aca="false">E3+F3-G3</f>
+        <v>1000</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="J3" s="24" t="str">
+        <f aca="false">IF($H3&lt;=$I3,"REPONER","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>800</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="22" t="n">
+        <f aca="false">SUMIF('Remisiones Insumos'!$E:$E,$B4,'Remisiones Insumos'!$F:$F)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="23" t="n">
+        <f aca="false">E4+F4-G4</f>
+        <v>800</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" s="24" t="str">
+        <f aca="false">IF($H4&lt;=$I4,"REPONER","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="22" t="n">
+        <f aca="false">SUMIF('Remisiones Insumos'!$E:$E,$B5,'Remisiones Insumos'!$F:$F)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="23" t="n">
+        <f aca="false">E5+F5-G5</f>
+        <v>1200</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="J5" s="24" t="str">
+        <f aca="false">IF($H5&lt;=$I5,"REPONER","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="22" t="n">
+        <f aca="false">SUMIF('Remisiones Insumos'!$E:$E,$B6,'Remisiones Insumos'!$F:$F)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="23" t="n">
+        <f aca="false">E6+F6-G6</f>
+        <v>3000</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="J6" s="24" t="str">
+        <f aca="false">IF($H6&lt;=$I6,"REPONER","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>600</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="22" t="n">
+        <f aca="false">SUMIF('Remisiones Insumos'!$E:$E,$B7,'Remisiones Insumos'!$F:$F)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="23" t="n">
+        <f aca="false">E7+F7-G7</f>
+        <v>600</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="J7" s="24" t="str">
+        <f aca="false">IF($H7&lt;=$I7,"REPONER","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <f aca="false">SUMIF('Remisiones Insumos'!$E:$E,$B8,'Remisiones Insumos'!$F:$F)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="23" t="n">
+        <f aca="false">E8+F8-G8</f>
+        <v>300</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="J8" s="24" t="str">
+        <f aca="false">IF($H8&lt;=$I8,"REPONER","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <f aca="false">SUMIF('Remisiones Insumos'!$E:$E,$B9,'Remisiones Insumos'!$F:$F)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <f aca="false">E9+F9-G9</f>
+        <v>200</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" s="24" t="str">
+        <f aca="false">IF($H9&lt;=$I9,"REPONER","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="C10" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="22" t="n">
+        <f aca="false">SUMIF('Remisiones Insumos'!$E:$E,$B10,'Remisiones Insumos'!$F:$F)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <f aca="false">E10+F10-G10</f>
+        <v>1000</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="J10" s="24" t="str">
+        <f aca="false">IF($H10&lt;=$I10,"REPONER","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="22" t="n">
+        <f aca="false">SUMIF('Remisiones Insumos'!$E:$E,$B11,'Remisiones Insumos'!$F:$F)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <f aca="false">E11+F11-G11</f>
+        <v>500</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="J11" s="24" t="str">
+        <f aca="false">IF($H11&lt;=$I11,"REPONER","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="22" t="n">
+        <f aca="false">SUMIF('Remisiones Insumos'!$E:$E,$B12,'Remisiones Insumos'!$F:$F)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="23" t="n">
+        <f aca="false">E12+F12-G12</f>
+        <v>1000</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" s="24" t="str">
+        <f aca="false">IF($H12&lt;=$I12,"REPONER","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>800</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="22" t="n">
+        <f aca="false">SUMIF('Remisiones Insumos'!$E:$E,$B13,'Remisiones Insumos'!$F:$F)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <f aca="false">E13+F13-G13</f>
+        <v>800</v>
+      </c>
+      <c r="I13" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="D2" s="21" t="n">
-        <v>30</v>
-      </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="J13" s="24" t="str">
+        <f aca="false">IF($H13&lt;=$I13,"REPONER","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="22" t="n">
+        <f aca="false">SUMIF('Remisiones Insumos'!$E:$E,$B14,'Remisiones Insumos'!$F:$F)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="23" t="n">
+        <f aca="false">E14+F14-G14</f>
+        <v>150</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="J14" s="24" t="str">
+        <f aca="false">IF($H14&lt;=$I14,"REPONER","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="22" t="n">
+        <f aca="false">SUMIF('Remisiones Insumos'!$E:$E,$B15,'Remisiones Insumos'!$F:$F)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="23" t="n">
+        <f aca="false">E15+F15-G15</f>
+        <v>700</v>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="J15" s="24" t="str">
+        <f aca="false">IF($H15&lt;=$I15,"REPONER","")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B2:B500" type="list">
-      <formula1>Inventario!$A$7:$A$11</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4238,13 +5321,13 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF213033"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G40"/>
@@ -4261,7 +5344,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -4271,73 +5354,73 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="22" t="s">
-        <v>83</v>
+      <c r="A2" s="25" t="s">
+        <v>118</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" s="23"/>
-      <c r="F2" s="22" t="s">
-        <v>87</v>
+        <v>119</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="26"/>
+      <c r="F2" s="25" t="s">
+        <v>122</v>
       </c>
       <c r="G2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
-        <v>88</v>
+      <c r="A3" s="25" t="s">
+        <v>123</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>90</v>
+        <v>124</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>125</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3" s="24" t="n">
+        <v>126</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="27" t="n">
         <v>0.19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>99</v>
+      <c r="A5" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>101</v>
+      <c r="A6" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>136</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>15900</v>
@@ -4345,23 +5428,23 @@
       <c r="D6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="E6" s="31" t="n">
         <f aca="false">ROUND(F6*$G$3,0)</f>
         <v>3021</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="31" t="n">
         <f aca="false">C6*D6</f>
         <v>15900</v>
       </c>
-      <c r="G6" s="28" t="n">
+      <c r="G6" s="31" t="n">
         <f aca="false">F6+E6</f>
         <v>18921</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26"/>
-      <c r="B7" s="27" t="s">
-        <v>102</v>
+      <c r="A7" s="29"/>
+      <c r="B7" s="30" t="s">
+        <v>137</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>0</v>
@@ -4369,25 +5452,25 @@
       <c r="D7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="28" t="n">
+      <c r="E7" s="31" t="n">
         <f aca="false">ROUND(F7*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="28" t="n">
+      <c r="F7" s="31" t="n">
         <f aca="false">C7*D7</f>
         <v>0</v>
       </c>
-      <c r="G7" s="28" t="n">
+      <c r="G7" s="31" t="n">
         <f aca="false">F7+E7</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>88</v>
+      <c r="A8" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>123</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>15900</v>
@@ -4395,23 +5478,23 @@
       <c r="D8" s="9" t="n">
         <v>1.07</v>
       </c>
-      <c r="E8" s="28" t="n">
+      <c r="E8" s="31" t="n">
         <f aca="false">ROUND(F8*$G$3,0)</f>
         <v>3232</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="31" t="n">
         <f aca="false">C8*D8</f>
         <v>17013</v>
       </c>
-      <c r="G8" s="28" t="n">
+      <c r="G8" s="31" t="n">
         <f aca="false">F8+E8</f>
         <v>20245</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26"/>
-      <c r="B9" s="27" t="s">
-        <v>104</v>
+      <c r="A9" s="29"/>
+      <c r="B9" s="30" t="s">
+        <v>139</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>4400</v>
@@ -4419,23 +5502,23 @@
       <c r="D9" s="9" t="n">
         <v>0.15</v>
       </c>
-      <c r="E9" s="28" t="n">
+      <c r="E9" s="31" t="n">
         <f aca="false">ROUND(F9*$G$3,0)</f>
         <v>125</v>
       </c>
-      <c r="F9" s="28" t="n">
+      <c r="F9" s="31" t="n">
         <f aca="false">C9*D9</f>
         <v>660</v>
       </c>
-      <c r="G9" s="28" t="n">
+      <c r="G9" s="31" t="n">
         <f aca="false">F9+E9</f>
         <v>785</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26"/>
-      <c r="B10" s="27" t="s">
-        <v>105</v>
+      <c r="A10" s="29"/>
+      <c r="B10" s="30" t="s">
+        <v>140</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>0</v>
@@ -4443,25 +5526,25 @@
       <c r="D10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="28" t="n">
+      <c r="E10" s="31" t="n">
         <f aca="false">ROUND(F10*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="28" t="n">
+      <c r="F10" s="31" t="n">
         <f aca="false">C10*D10</f>
         <v>0</v>
       </c>
-      <c r="G10" s="28" t="n">
+      <c r="G10" s="31" t="n">
         <f aca="false">F10+E10</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>107</v>
+      <c r="A11" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>142</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>0</v>
@@ -4469,23 +5552,23 @@
       <c r="D11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="28" t="n">
+      <c r="E11" s="31" t="n">
         <f aca="false">ROUND(F11*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="28" t="n">
+      <c r="F11" s="31" t="n">
         <f aca="false">C11*D11</f>
         <v>0</v>
       </c>
-      <c r="G11" s="28" t="n">
+      <c r="G11" s="31" t="n">
         <f aca="false">F11+E11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27" t="s">
-        <v>108</v>
+      <c r="A12" s="29"/>
+      <c r="B12" s="30" t="s">
+        <v>143</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>1200</v>
@@ -4493,25 +5576,25 @@
       <c r="D12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="28" t="n">
+      <c r="E12" s="31" t="n">
         <f aca="false">ROUND(F12*$G$3,0)</f>
         <v>228</v>
       </c>
-      <c r="F12" s="28" t="n">
+      <c r="F12" s="31" t="n">
         <f aca="false">C12*D12</f>
         <v>1200</v>
       </c>
-      <c r="G12" s="28" t="n">
+      <c r="G12" s="31" t="n">
         <f aca="false">F12+E12</f>
         <v>1428</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="B13" s="27" t="s">
-        <v>110</v>
+      <c r="A13" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>145</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>10700</v>
@@ -4519,25 +5602,25 @@
       <c r="D13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="28" t="n">
+      <c r="E13" s="31" t="n">
         <f aca="false">ROUND(F13*$G$3,0)</f>
         <v>2033</v>
       </c>
-      <c r="F13" s="28" t="n">
+      <c r="F13" s="31" t="n">
         <f aca="false">C13*D13</f>
         <v>10700</v>
       </c>
-      <c r="G13" s="28" t="n">
+      <c r="G13" s="31" t="n">
         <f aca="false">F13+E13</f>
         <v>12733</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>112</v>
+      <c r="A14" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>147</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>700</v>
@@ -4545,23 +5628,23 @@
       <c r="D14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="28" t="n">
+      <c r="E14" s="31" t="n">
         <f aca="false">ROUND(F14*$G$3,0)</f>
         <v>133</v>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="31" t="n">
         <f aca="false">C14*D14</f>
         <v>700</v>
       </c>
-      <c r="G14" s="28" t="n">
+      <c r="G14" s="31" t="n">
         <f aca="false">F14+E14</f>
         <v>833</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27" t="s">
-        <v>113</v>
+      <c r="A15" s="29"/>
+      <c r="B15" s="30" t="s">
+        <v>148</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>87</v>
@@ -4569,23 +5652,23 @@
       <c r="D15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="28" t="n">
+      <c r="E15" s="31" t="n">
         <f aca="false">ROUND(F15*$G$3,0)</f>
         <v>17</v>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F15" s="31" t="n">
         <f aca="false">C15*D15</f>
         <v>87</v>
       </c>
-      <c r="G15" s="28" t="n">
+      <c r="G15" s="31" t="n">
         <f aca="false">F15+E15</f>
         <v>104</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27" t="s">
-        <v>114</v>
+      <c r="A16" s="29"/>
+      <c r="B16" s="30" t="s">
+        <v>149</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>0</v>
@@ -4593,25 +5676,25 @@
       <c r="D16" s="9" t="n">
         <v>0.07</v>
       </c>
-      <c r="E16" s="28" t="n">
+      <c r="E16" s="31" t="n">
         <f aca="false">ROUND(F16*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F16" s="31" t="n">
         <f aca="false">C16*D16</f>
         <v>0</v>
       </c>
-      <c r="G16" s="28" t="n">
+      <c r="G16" s="31" t="n">
         <f aca="false">F16+E16</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>115</v>
+      <c r="A17" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>150</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>7000</v>
@@ -4619,23 +5702,23 @@
       <c r="D17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="28" t="n">
+      <c r="E17" s="31" t="n">
         <f aca="false">ROUND(F17*$G$3,0)</f>
         <v>1330</v>
       </c>
-      <c r="F17" s="28" t="n">
+      <c r="F17" s="31" t="n">
         <f aca="false">C17*D17</f>
         <v>7000</v>
       </c>
-      <c r="G17" s="28" t="n">
+      <c r="G17" s="31" t="n">
         <f aca="false">F17+E17</f>
         <v>8330</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="26"/>
-      <c r="B18" s="27" t="s">
-        <v>116</v>
+      <c r="A18" s="29"/>
+      <c r="B18" s="30" t="s">
+        <v>151</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>2100</v>
@@ -4643,25 +5726,25 @@
       <c r="D18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="28" t="n">
+      <c r="E18" s="31" t="n">
         <f aca="false">ROUND(F18*$G$3,0)</f>
         <v>399</v>
       </c>
-      <c r="F18" s="28" t="n">
+      <c r="F18" s="31" t="n">
         <f aca="false">C18*D18</f>
         <v>2100</v>
       </c>
-      <c r="G18" s="28" t="n">
+      <c r="G18" s="31" t="n">
         <f aca="false">F18+E18</f>
         <v>2499</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>118</v>
+      <c r="A19" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>153</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>20</v>
@@ -4669,23 +5752,23 @@
       <c r="D19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="28" t="n">
+      <c r="E19" s="31" t="n">
         <f aca="false">ROUND(F19*$G$3,0)</f>
         <v>4</v>
       </c>
-      <c r="F19" s="28" t="n">
+      <c r="F19" s="31" t="n">
         <f aca="false">C19*D19</f>
         <v>20</v>
       </c>
-      <c r="G19" s="28" t="n">
+      <c r="G19" s="31" t="n">
         <f aca="false">F19+E19</f>
         <v>24</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27" t="s">
-        <v>119</v>
+      <c r="A20" s="29"/>
+      <c r="B20" s="30" t="s">
+        <v>154</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>123</v>
@@ -4693,23 +5776,23 @@
       <c r="D20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="28" t="n">
+      <c r="E20" s="31" t="n">
         <f aca="false">ROUND(F20*$G$3,0)</f>
         <v>23</v>
       </c>
-      <c r="F20" s="28" t="n">
+      <c r="F20" s="31" t="n">
         <f aca="false">C20*D20</f>
         <v>123</v>
       </c>
-      <c r="G20" s="28" t="n">
+      <c r="G20" s="31" t="n">
         <f aca="false">F20+E20</f>
         <v>146</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27" t="s">
-        <v>120</v>
+      <c r="A21" s="29"/>
+      <c r="B21" s="30" t="s">
+        <v>155</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>10</v>
@@ -4717,23 +5800,23 @@
       <c r="D21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="28" t="n">
+      <c r="E21" s="31" t="n">
         <f aca="false">ROUND(F21*$G$3,0)</f>
         <v>2</v>
       </c>
-      <c r="F21" s="28" t="n">
+      <c r="F21" s="31" t="n">
         <f aca="false">C21*D21</f>
         <v>10</v>
       </c>
-      <c r="G21" s="28" t="n">
+      <c r="G21" s="31" t="n">
         <f aca="false">F21+E21</f>
         <v>12</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27" t="s">
-        <v>121</v>
+      <c r="A22" s="29"/>
+      <c r="B22" s="30" t="s">
+        <v>156</v>
       </c>
       <c r="C22" s="8" t="n">
         <v>180</v>
@@ -4741,25 +5824,25 @@
       <c r="D22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="28" t="n">
+      <c r="E22" s="31" t="n">
         <f aca="false">ROUND(F22*$G$3,0)</f>
         <v>34</v>
       </c>
-      <c r="F22" s="28" t="n">
+      <c r="F22" s="31" t="n">
         <f aca="false">C22*D22</f>
         <v>180</v>
       </c>
-      <c r="G22" s="28" t="n">
+      <c r="G22" s="31" t="n">
         <f aca="false">F22+E22</f>
         <v>214</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>123</v>
+      <c r="A23" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>158</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>278</v>
@@ -4767,23 +5850,23 @@
       <c r="D23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="28" t="n">
+      <c r="E23" s="31" t="n">
         <f aca="false">ROUND(F23*$G$3,0)</f>
         <v>53</v>
       </c>
-      <c r="F23" s="28" t="n">
+      <c r="F23" s="31" t="n">
         <f aca="false">C23*D23</f>
         <v>278</v>
       </c>
-      <c r="G23" s="28" t="n">
+      <c r="G23" s="31" t="n">
         <f aca="false">F23+E23</f>
         <v>331</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27" t="s">
-        <v>124</v>
+      <c r="A24" s="29"/>
+      <c r="B24" s="30" t="s">
+        <v>159</v>
       </c>
       <c r="C24" s="8" t="n">
         <v>111</v>
@@ -4791,23 +5874,23 @@
       <c r="D24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="28" t="n">
+      <c r="E24" s="31" t="n">
         <f aca="false">ROUND(F24*$G$3,0)</f>
         <v>42</v>
       </c>
-      <c r="F24" s="28" t="n">
+      <c r="F24" s="31" t="n">
         <f aca="false">C24*D24</f>
         <v>222</v>
       </c>
-      <c r="G24" s="28" t="n">
+      <c r="G24" s="31" t="n">
         <f aca="false">F24+E24</f>
         <v>264</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26"/>
-      <c r="B25" s="27" t="s">
-        <v>125</v>
+      <c r="A25" s="29"/>
+      <c r="B25" s="30" t="s">
+        <v>160</v>
       </c>
       <c r="C25" s="8" t="n">
         <v>700</v>
@@ -4815,23 +5898,23 @@
       <c r="D25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="28" t="n">
+      <c r="E25" s="31" t="n">
         <f aca="false">ROUND(F25*$G$3,0)</f>
         <v>133</v>
       </c>
-      <c r="F25" s="28" t="n">
+      <c r="F25" s="31" t="n">
         <f aca="false">C25*D25</f>
         <v>700</v>
       </c>
-      <c r="G25" s="28" t="n">
+      <c r="G25" s="31" t="n">
         <f aca="false">F25+E25</f>
         <v>833</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27" t="s">
-        <v>126</v>
+      <c r="A26" s="29"/>
+      <c r="B26" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="C26" s="8" t="n">
         <v>0</v>
@@ -4839,23 +5922,23 @@
       <c r="D26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="28" t="n">
+      <c r="E26" s="31" t="n">
         <f aca="false">ROUND(F26*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F26" s="28" t="n">
+      <c r="F26" s="31" t="n">
         <f aca="false">C26*D26</f>
         <v>0</v>
       </c>
-      <c r="G26" s="28" t="n">
+      <c r="G26" s="31" t="n">
         <f aca="false">F26+E26</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="26"/>
-      <c r="B27" s="27" t="s">
-        <v>127</v>
+      <c r="A27" s="29"/>
+      <c r="B27" s="30" t="s">
+        <v>162</v>
       </c>
       <c r="C27" s="8" t="n">
         <v>0</v>
@@ -4863,25 +5946,25 @@
       <c r="D27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="28" t="n">
+      <c r="E27" s="31" t="n">
         <f aca="false">ROUND(F27*$G$3,0)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="28" t="n">
+      <c r="F27" s="31" t="n">
         <f aca="false">C27*D27</f>
         <v>0</v>
       </c>
-      <c r="G27" s="28" t="n">
+      <c r="G27" s="31" t="n">
         <f aca="false">F27+E27</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="B28" s="27" t="s">
-        <v>128</v>
+      <c r="A28" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>163</v>
       </c>
       <c r="C28" s="8" t="n">
         <v>11000</v>
@@ -4889,154 +5972,154 @@
       <c r="D28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="28" t="n">
+      <c r="E28" s="31" t="n">
         <f aca="false">ROUND(F28*$G$3,0)</f>
         <v>2090</v>
       </c>
-      <c r="F28" s="28" t="n">
+      <c r="F28" s="31" t="n">
         <f aca="false">C28*D28</f>
         <v>11000</v>
       </c>
-      <c r="G28" s="28" t="n">
+      <c r="G28" s="31" t="n">
         <f aca="false">F28+E28</f>
         <v>13090</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="29"/>
-      <c r="B29" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="31" t="n">
+      <c r="A29" s="32"/>
+      <c r="B29" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="34" t="n">
         <f aca="false">SUM(F6:F28)</f>
         <v>67893</v>
       </c>
-      <c r="G29" s="31" t="n">
+      <c r="G29" s="34" t="n">
         <f aca="false">SUM(G6:G28)</f>
         <v>80792</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="B32" s="32" t="n">
+      <c r="A32" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="B32" s="35" t="n">
         <f aca="false">F29</f>
         <v>67893</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="B33" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="C33" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="E33" s="25" t="s">
-        <v>136</v>
+      <c r="A33" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="E33" s="28" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="24" t="n">
+      <c r="A34" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="B34" s="33" t="n">
+      <c r="B34" s="23" t="n">
         <f aca="false">ROUND($B$32*(1+A34)*(1+$G$3),0)</f>
         <v>121189</v>
       </c>
-      <c r="C34" s="34" t="n">
+      <c r="C34" s="36" t="n">
         <f aca="false">ROUND(B34/(1+$G$3),0)</f>
         <v>101839</v>
       </c>
-      <c r="D34" s="35" t="n">
+      <c r="D34" s="22" t="n">
         <f aca="false">B34-C34</f>
         <v>19350</v>
       </c>
-      <c r="E34" s="36" t="n">
+      <c r="E34" s="37" t="n">
         <f aca="false">IF(C34=0,0,(C34-$B$32)/C34)</f>
         <v>0.33333006019305</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="24" t="n">
+      <c r="A35" s="27" t="n">
         <v>0.65</v>
       </c>
-      <c r="B35" s="33" t="n">
+      <c r="B35" s="23" t="n">
         <f aca="false">ROUND($B$32*(1+A35)*(1+$G$3),0)</f>
         <v>133308</v>
       </c>
-      <c r="C35" s="34" t="n">
+      <c r="C35" s="36" t="n">
         <f aca="false">ROUND(B35/(1+$G$3),0)</f>
         <v>112024</v>
       </c>
-      <c r="D35" s="35" t="n">
+      <c r="D35" s="22" t="n">
         <f aca="false">B35-C35</f>
         <v>21284</v>
       </c>
-      <c r="E35" s="36" t="n">
+      <c r="E35" s="37" t="n">
         <f aca="false">IF(C35=0,0,(C35-$B$32)/C35)</f>
         <v>0.393942369492252</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="24" t="n">
+      <c r="A36" s="27" t="n">
         <v>0.8</v>
       </c>
-      <c r="B36" s="33" t="n">
+      <c r="B36" s="23" t="n">
         <f aca="false">ROUND($B$32*(1+A36)*(1+$G$3),0)</f>
         <v>145427</v>
       </c>
-      <c r="C36" s="34" t="n">
+      <c r="C36" s="36" t="n">
         <f aca="false">ROUND(B36/(1+$G$3),0)</f>
         <v>122208</v>
       </c>
-      <c r="D36" s="35" t="n">
+      <c r="D36" s="22" t="n">
         <f aca="false">B36-C36</f>
         <v>23219</v>
       </c>
-      <c r="E36" s="36" t="n">
+      <c r="E36" s="37" t="n">
         <f aca="false">IF(C36=0,0,(C36-$B$32)/C36)</f>
         <v>0.444447172034564</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="22" t="s">
-        <v>137</v>
+      <c r="A38" s="25" t="s">
+        <v>172</v>
       </c>
       <c r="B38" s="7"/>
-      <c r="C38" s="22" t="s">
-        <v>138</v>
+      <c r="C38" s="25" t="s">
+        <v>173</v>
       </c>
       <c r="D38" s="7"/>
-      <c r="F38" s="22" t="s">
-        <v>139</v>
+      <c r="F38" s="25" t="s">
+        <v>174</v>
       </c>
       <c r="G38" s="7"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="37" t="s">
-        <v>140</v>
-      </c>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="37"/>
+      <c r="A40" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="B40" s="38"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -5071,395 +6154,408 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF213033"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="38" t="s">
-        <v>150</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="16"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="38" t="s">
-        <v>154</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
       <c r="E1" s="13"/>
       <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="39" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="B2" s="39"/>
       <c r="C2" s="39"/>
       <c r="D2" s="39"/>
       <c r="E2" s="39"/>
       <c r="F2" s="39"/>
-    </row>
-    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="22" t="s">
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+    </row>
+    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" s="40" t="str">
+        <f aca="false">"OC-2026-"&amp;TEXT(COUNTA('Histórico Cortes'!$B$3:$B$5000)+1,"0000")</f>
+        <v>OC-2026-0001</v>
+      </c>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+    </row>
+    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="7"/>
-    </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="40" t="s">
+      <c r="B5" s="41" t="n">
+        <f aca="true">TODAY()</f>
+        <v>46204</v>
+      </c>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+    </row>
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="D6" s="41" t="n">
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+    </row>
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="B7" s="43" t="n">
         <f aca="false">IFERROR(VLOOKUP(B6,Inventario!$A$7:$E$20,5,0),0)</f>
         <v>69</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="D7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42" t="s">
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+    </row>
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="H11" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="I11" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="K11" s="28" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="44"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="31" t="str">
+        <f aca="false">IF($A12="","",SUM(B12:H12))</f>
+        <v/>
+      </c>
+      <c r="J12" s="46"/>
+      <c r="K12" s="19" t="str">
+        <f aca="false">IF(OR($I12=0,$J12=""),"",$I12*$J12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="44"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="31" t="str">
+        <f aca="false">IF($A13="","",SUM(B13:H13))</f>
+        <v/>
+      </c>
+      <c r="J13" s="46"/>
+      <c r="K13" s="19" t="str">
+        <f aca="false">IF(OR($I13=0,$J13=""),"",$I13*$J13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="44"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="31" t="str">
+        <f aca="false">IF($A14="","",SUM(B14:H14))</f>
+        <v/>
+      </c>
+      <c r="J14" s="46"/>
+      <c r="K14" s="19" t="str">
+        <f aca="false">IF(OR($I14=0,$J14=""),"",$I14*$J14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="44"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="31" t="str">
+        <f aca="false">IF($A15="","",SUM(B15:H15))</f>
+        <v/>
+      </c>
+      <c r="J15" s="46"/>
+      <c r="K15" s="19" t="str">
+        <f aca="false">IF(OR($I15=0,$J15=""),"",$I15*$J15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="44"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="31" t="str">
+        <f aca="false">IF($A16="","",SUM(B16:H16))</f>
+        <v/>
+      </c>
+      <c r="J16" s="46"/>
+      <c r="K16" s="19" t="str">
+        <f aca="false">IF(OR($I16=0,$J16=""),"",$I16*$J16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="48" t="n">
+        <f aca="false">SUM(B12:B16)</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="48" t="n">
+        <f aca="false">SUM(C12:C16)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="48" t="n">
+        <f aca="false">SUM(D12:D16)</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="48" t="n">
+        <f aca="false">SUM(E12:E16)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="48" t="n">
+        <f aca="false">SUM(F12:F16)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="48" t="n">
+        <f aca="false">SUM(G12:G16)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="48" t="n">
+        <f aca="false">SUM(H12:H16)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="34" t="n">
+        <f aca="false">SUM(I12:I16)</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="32"/>
+      <c r="K17" s="49" t="n">
+        <f aca="false">SUM(K12:K16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="42" t="s">
+      <c r="B20" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="42" t="s">
+      <c r="C20" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="42" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="43"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-    </row>
-    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="43"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-    </row>
-    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="43"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-    </row>
-    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="43"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-    </row>
-    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="D17" s="7"/>
-    </row>
-    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="D18" s="7"/>
-    </row>
-    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="D19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="D20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="B23" s="42" t="s">
-        <v>172</v>
-      </c>
-      <c r="C23" s="42" t="s">
-        <v>173</v>
-      </c>
-      <c r="D23" s="42" t="s">
-        <v>174</v>
-      </c>
-      <c r="E23" s="42" t="s">
-        <v>175</v>
-      </c>
-      <c r="F23" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="G23" s="42" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="44"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-    </row>
-    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="45" t="s">
-        <v>179</v>
-      </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-    </row>
-    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="45"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-    </row>
-    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="45"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-    </row>
-    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="22" t="s">
-        <v>180</v>
-      </c>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="E31" s="7"/>
+      <c r="D20" s="50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="51" t="str">
+        <f aca="false">IFERROR(filter('Órdenes de Ingreso'!O2:O201,'Órdenes de Ingreso'!K2:K201=$B$6),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="B21" s="51" t="str">
+        <f aca="false">IFERROR(filter('Órdenes de Ingreso'!H2:H201,'Órdenes de Ingreso'!K2:K201=$B$6),"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="51" t="str">
+        <f aca="false">IFERROR(filter('Órdenes de Ingreso'!I2:I201,'Órdenes de Ingreso'!K2:K201=$B$6),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="51" t="str">
+        <f aca="false">IFERROR(filter('Órdenes de Ingreso'!M2:M201,'Órdenes de Ingreso'!K2:K201=$B$6),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="B30" s="52"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+    </row>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="52"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="52"/>
+      <c r="K31" s="52"/>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="52"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+    </row>
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A27:F29"/>
-    <mergeCell ref="B31:C31"/>
+  <mergeCells count="10">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A30:K32"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="G34:H34"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B6" type="list">
       <formula1>Inventario!$A$7:$A$11</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E31" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G34" type="list">
       <formula1>"Borrador,Autorizada,En proceso,Cortada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5473,4 +6569,651 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF213033"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="7"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="7"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="21" t="str">
+        <f aca="false">IFERROR(VLOOKUP($A7,'Inventario de Insumos'!$B:$D,3,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="21" t="str">
+        <f aca="false">IFERROR(VLOOKUP($A8,'Inventario de Insumos'!$B:$D,3,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="21" t="str">
+        <f aca="false">IFERROR(VLOOKUP($A9,'Inventario de Insumos'!$B:$D,3,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="21" t="str">
+        <f aca="false">IFERROR(VLOOKUP($A10,'Inventario de Insumos'!$B:$D,3,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="21" t="str">
+        <f aca="false">IFERROR(VLOOKUP($A11,'Inventario de Insumos'!$B:$D,3,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="21" t="str">
+        <f aca="false">IFERROR(VLOOKUP($A12,'Inventario de Insumos'!$B:$D,3,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="21" t="str">
+        <f aca="false">IFERROR(VLOOKUP($A13,'Inventario de Insumos'!$B:$D,3,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="21" t="str">
+        <f aca="false">IFERROR(VLOOKUP($A14,'Inventario de Insumos'!$B:$D,3,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="21" t="str">
+        <f aca="false">IFERROR(VLOOKUP($A15,'Inventario de Insumos'!$B:$D,3,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="21" t="str">
+        <f aca="false">IFERROR(VLOOKUP($A16,'Inventario de Insumos'!$B:$D,3,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A20:E20"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B3" type="list">
+      <formula1>"Confeccionista,Terminación"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A7:A16" type="list">
+      <formula1>'Inventario de Insumos'!$B$2:$B$30</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF87A6B8"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="54" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B5" s="55" t="n">
+        <f aca="false">IF($A5="","",COUNTIF('Histórico Cortes'!$C:$C,$A5))</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="56" t="n">
+        <f aca="false">IF($A5="","",SUMIF('Histórico Cortes'!$C:$C,$A5,'Histórico Cortes'!$M:$M))</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="56" t="n">
+        <f aca="false">IF($A5="","",SUMIF('Histórico Cortes'!$C:$C,$A5,'Histórico Cortes'!$O:$O))</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="56" t="n">
+        <f aca="false">IF($A5="","",SUMIF('Histórico Cortes'!$C:$C,$A5,'Histórico Cortes'!$P:$P))</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="57" t="n">
+        <f aca="false">IF($A5="","",$E5-$D5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B6" s="55" t="n">
+        <f aca="false">IF($A6="","",COUNTIF('Histórico Cortes'!$C:$C,$A6))</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="56" t="n">
+        <f aca="false">IF($A6="","",SUMIF('Histórico Cortes'!$C:$C,$A6,'Histórico Cortes'!$M:$M))</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="56" t="n">
+        <f aca="false">IF($A6="","",SUMIF('Histórico Cortes'!$C:$C,$A6,'Histórico Cortes'!$O:$O))</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="56" t="n">
+        <f aca="false">IF($A6="","",SUMIF('Histórico Cortes'!$C:$C,$A6,'Histórico Cortes'!$P:$P))</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="57" t="n">
+        <f aca="false">IF($A6="","",$E6-$D6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="B7" s="55" t="n">
+        <f aca="false">IF($A7="","",COUNTIF('Histórico Cortes'!$C:$C,$A7))</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="56" t="n">
+        <f aca="false">IF($A7="","",SUMIF('Histórico Cortes'!$C:$C,$A7,'Histórico Cortes'!$M:$M))</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="56" t="n">
+        <f aca="false">IF($A7="","",SUMIF('Histórico Cortes'!$C:$C,$A7,'Histórico Cortes'!$O:$O))</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="56" t="n">
+        <f aca="false">IF($A7="","",SUMIF('Histórico Cortes'!$C:$C,$A7,'Histórico Cortes'!$P:$P))</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="57" t="n">
+        <f aca="false">IF($A7="","",$E7-$D7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7"/>
+      <c r="B8" s="55" t="str">
+        <f aca="false">IF($A8="","",COUNTIF('Histórico Cortes'!$C:$C,$A8))</f>
+        <v/>
+      </c>
+      <c r="C8" s="56" t="str">
+        <f aca="false">IF($A8="","",SUMIF('Histórico Cortes'!$C:$C,$A8,'Histórico Cortes'!$M:$M))</f>
+        <v/>
+      </c>
+      <c r="D8" s="56" t="str">
+        <f aca="false">IF($A8="","",SUMIF('Histórico Cortes'!$C:$C,$A8,'Histórico Cortes'!$O:$O))</f>
+        <v/>
+      </c>
+      <c r="E8" s="56" t="str">
+        <f aca="false">IF($A8="","",SUMIF('Histórico Cortes'!$C:$C,$A8,'Histórico Cortes'!$P:$P))</f>
+        <v/>
+      </c>
+      <c r="F8" s="57" t="str">
+        <f aca="false">IF($A8="","",$E8-$D8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7"/>
+      <c r="B9" s="55" t="str">
+        <f aca="false">IF($A9="","",COUNTIF('Histórico Cortes'!$C:$C,$A9))</f>
+        <v/>
+      </c>
+      <c r="C9" s="56" t="str">
+        <f aca="false">IF($A9="","",SUMIF('Histórico Cortes'!$C:$C,$A9,'Histórico Cortes'!$M:$M))</f>
+        <v/>
+      </c>
+      <c r="D9" s="56" t="str">
+        <f aca="false">IF($A9="","",SUMIF('Histórico Cortes'!$C:$C,$A9,'Histórico Cortes'!$O:$O))</f>
+        <v/>
+      </c>
+      <c r="E9" s="56" t="str">
+        <f aca="false">IF($A9="","",SUMIF('Histórico Cortes'!$C:$C,$A9,'Histórico Cortes'!$P:$P))</f>
+        <v/>
+      </c>
+      <c r="F9" s="57" t="str">
+        <f aca="false">IF($A9="","",$E9-$D9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="54" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="B14" s="55" t="n">
+        <f aca="false">IF($A14="","",COUNTIF('Histórico Cortes'!$R:$R,$A14))</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="56" t="n">
+        <f aca="false">IF($A14="","",SUMIF('Histórico Cortes'!$R:$R,$A14,'Histórico Cortes'!$M:$M))</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="56" t="n">
+        <f aca="false">IF($A14="","",SUMIF('Histórico Cortes'!$R:$R,$A14,'Histórico Cortes'!$O:$O))</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="56" t="n">
+        <f aca="false">IF($A14="","",SUMIF('Histórico Cortes'!$R:$R,$A14,'Histórico Cortes'!$P:$P))</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="57" t="n">
+        <f aca="false">IF($A14="","",$E14-$D14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B15" s="55" t="n">
+        <f aca="false">IF($A15="","",COUNTIF('Histórico Cortes'!$R:$R,$A15))</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="56" t="n">
+        <f aca="false">IF($A15="","",SUMIF('Histórico Cortes'!$R:$R,$A15,'Histórico Cortes'!$M:$M))</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="56" t="n">
+        <f aca="false">IF($A15="","",SUMIF('Histórico Cortes'!$R:$R,$A15,'Histórico Cortes'!$O:$O))</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="56" t="n">
+        <f aca="false">IF($A15="","",SUMIF('Histórico Cortes'!$R:$R,$A15,'Histórico Cortes'!$P:$P))</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="57" t="n">
+        <f aca="false">IF($A15="","",$E15-$D15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7"/>
+      <c r="B16" s="55" t="str">
+        <f aca="false">IF($A16="","",COUNTIF('Histórico Cortes'!$R:$R,$A16))</f>
+        <v/>
+      </c>
+      <c r="C16" s="56" t="str">
+        <f aca="false">IF($A16="","",SUMIF('Histórico Cortes'!$R:$R,$A16,'Histórico Cortes'!$M:$M))</f>
+        <v/>
+      </c>
+      <c r="D16" s="56" t="str">
+        <f aca="false">IF($A16="","",SUMIF('Histórico Cortes'!$R:$R,$A16,'Histórico Cortes'!$O:$O))</f>
+        <v/>
+      </c>
+      <c r="E16" s="56" t="str">
+        <f aca="false">IF($A16="","",SUMIF('Histórico Cortes'!$R:$R,$A16,'Histórico Cortes'!$P:$P))</f>
+        <v/>
+      </c>
+      <c r="F16" s="57" t="str">
+        <f aca="false">IF($A16="","",$E16-$D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7"/>
+      <c r="B17" s="55" t="str">
+        <f aca="false">IF($A17="","",COUNTIF('Histórico Cortes'!$R:$R,$A17))</f>
+        <v/>
+      </c>
+      <c r="C17" s="56" t="str">
+        <f aca="false">IF($A17="","",SUMIF('Histórico Cortes'!$R:$R,$A17,'Histórico Cortes'!$M:$M))</f>
+        <v/>
+      </c>
+      <c r="D17" s="56" t="str">
+        <f aca="false">IF($A17="","",SUMIF('Histórico Cortes'!$R:$R,$A17,'Histórico Cortes'!$O:$O))</f>
+        <v/>
+      </c>
+      <c r="E17" s="56" t="str">
+        <f aca="false">IF($A17="","",SUMIF('Histórico Cortes'!$R:$R,$A17,'Histórico Cortes'!$P:$P))</f>
+        <v/>
+      </c>
+      <c r="F17" s="57" t="str">
+        <f aca="false">IF($A17="","",$E17-$D17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="58" t="s">
+        <v>221</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF606060"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D2" s="59" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B2:B500" type="list">
+      <formula1>Inventario!$A$7:$A$11</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>